--- a/CBT_2025_1회/산업안전기사_2025_1회_문항등록.xlsx
+++ b/CBT_2025_1회/산업안전기사_2025_1회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AG9" s="32" t="inlineStr">
         <is>
-          <t>말초운동 기능은 야간에 &lt;strong&gt;저하&lt;/strong&gt; 된다. 밤에 손발이 굼떠지는 것이 그 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주간과 야간의 생체리듬&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;주간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;야간&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체온 · 혈압 · 맥박수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;증가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;말초운동 기능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;혈액의 수분 · 염분량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>말초운동 기능은 야간에 &lt;strong&gt;저하&lt;/strong&gt;된다. 밤에 손발이 굼떠지는 것이 그 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주간과 야간의 생체리듬&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;주간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;야간&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체온 · 혈압 · 맥박수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;증가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;말초운동 기능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;혈액의 수분 · 염분량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH9" s="32" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="AG10" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;P 는 Person, 곧 개체(소질)&lt;/strong&gt;다. 소질·성격·지능·경험처럼 &lt;strong&gt;사람이 지닌 것&lt;/strong&gt;을 가리킨다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;$B = f ( P \cdot E )$ 의 각 문자&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;문자&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇이 드나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior&lt;/u&gt; · 행동&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;겉으로 드러난 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function&lt;/u&gt; · 함수&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;곱의 관계&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person&lt;/u&gt; · &lt;u&gt;개체(소질)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소질 · 성격 · 지능 · 경험 · 연령 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment&lt;/u&gt; · 환경&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계 · 작업환경 · 설비 · 감독&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_01_008_exp1.png"&gt;&lt;em&gt;레빈의 장 이론 — 행동은 사람과 환경의 함수다&lt;/em&gt;</t>
+          <t>&lt;strong&gt;P는 Person, 곧 개체(소질)&lt;/strong&gt;다. 소질·성격·지능·경험처럼 &lt;strong&gt;사람이 지닌 것&lt;/strong&gt;을 가리킨다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;$B = f ( P \cdot E )$의 각 문자&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;문자&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇이 드나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior&lt;/u&gt; · 행동&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;겉으로 드러난 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function&lt;/u&gt; · 함수&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;곱의 관계&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person&lt;/u&gt; · &lt;u&gt;개체(소질)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소질 · 성격 · 지능 · 경험 · 연령 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment&lt;/u&gt; · 환경&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계 · 작업환경 · 설비 · 감독&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_01_008_exp1.png"&gt;&lt;em&gt;레빈의 장 이론 — 행동은 사람과 환경의 함수다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH10" s="32" t="inlineStr">
         <is>
-          <t>① 행동은 좌변의 B 다.&lt;br&gt;③ 환경은 E 다.&lt;br&gt;④ 함수는 f 다.</t>
+          <t>① 행동은 좌변의 B다.&lt;br&gt;③ 환경은 E다.&lt;br&gt;④ 함수는 f다.</t>
         </is>
       </c>
       <c r="AI10" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;레빈(K. Lewin)의 장(場) 이론&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;덧셈이 아니라 곱셈&lt;/strong&gt;이라는 점이 중요하다. 사람만 고치거나 환경만 고쳐서는 사고가 줄지 않는다는 뜻이 여기 담겨 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;P 는 사람, E 는 환경&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;레빈(K. Lewin)의 장(場) 이론&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;덧셈이 아니라 곱셈&lt;/strong&gt;이라는 점이 중요하다. 사람만 고치거나 환경만 고쳐서는 사고가 줄지 않는다는 뜻이 여기 담겨 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;P는 사람, E는 환경&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3648,17 +3648,17 @@
       </c>
       <c r="AG20" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;영구 일부 노동불능(4~14급)&lt;/strong&gt;은 &lt;strong&gt;등급별 근로손실일수를 그대로&lt;/strong&gt; 쓴다. &lt;strong&gt;300/365 를 곱하는 것은 일시 전노동불능(휴업)&lt;/strong&gt; 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근로손실일수의 환산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;근로손실일수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사망 · 영구 전노동불능 (1~3급)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7,500일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300/365 를 곱하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영구 일부 노동불능 (4~14급)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;등급별 일수 그대로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;14급은 &lt;u&gt;50일&lt;/u&gt; · 4급은 5,500일&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일시 전노동불능 (휴업)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휴업일수 × 300/365&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기에만 곱한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_01_018_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
+          <t>&lt;strong&gt;영구 일부 노동불능(4~14급)&lt;/strong&gt;은 &lt;strong&gt;등급별 근로손실일수를 그대로&lt;/strong&gt; 쓴다. &lt;strong&gt;300/365를 곱하는 것은 일시 전노동불능(휴업)&lt;/strong&gt;뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근로손실일수의 환산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;근로손실일수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사망 · 영구 전노동불능 (1~3급)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7,500일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300/365를 곱하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영구 일부 노동불능 (4~14급)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;등급별 일수 그대로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;14급은 &lt;u&gt;50일&lt;/u&gt; · 4급은 5,500일&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일시 전노동불능 (휴업)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휴업일수 × 300/365&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기에만 곱한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_01_018_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH20" s="32" t="inlineStr">
         <is>
-          <t>① 사망과 1~3급은 7,500일로 환산한다.&lt;br&gt;② 제14급은 50일로 환산한다.&lt;br&gt;④ 일시 전노동불능은 휴업일수에 300/365 를 곱한다.</t>
+          <t>① 사망과 1~3급은 7,500일로 환산한다.&lt;br&gt;② 제14급은 50일로 환산한다.&lt;br&gt;④ 일시 전노동불능은 휴업일수에 300/365를 곱한다.</t>
         </is>
       </c>
       <c r="AI20" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;근로손실일수의 산정&lt;/strong&gt;&lt;br&gt;$\text{강도율} = \dfrac{\text{근로손실일수}}{\text{연근로시간}} \times 1 {,} 000$ 이다. &lt;strong&gt;300/365 는 「연간 근로일수 ÷ 연간 일수」&lt;/strong&gt;로, &lt;strong&gt;실제로 일했을 날만 세려고&lt;/strong&gt; 곱하는 것이다. 이미 일수로 정해진 장해등급에는 곱하지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;휴업일수에만 300/365&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;근로손실일수의 산정&lt;/strong&gt;&lt;br&gt;$\text{강도율} = \dfrac{\text{근로손실일수}}{\text{연근로시간}} \times 1 {,} 000$이다. &lt;strong&gt;300/365는 「연간 근로일수 ÷ 연간 일수」&lt;/strong&gt;로, &lt;strong&gt;실제로 일했을 날만 세려고&lt;/strong&gt; 곱하는 것이다. 이미 일수로 정해진 장해등급에는 곱하지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;휴업일수에만 300/365&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;고장이 발생하지 않도록 하는 집합&lt;/strong&gt;은 &lt;strong&gt;패스셋&lt;/strong&gt;이다. 최소 컷셋은 반대로 &lt;strong&gt;고장을 일으키는&lt;/strong&gt; 최소한의 집합이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;컷셋과 패스셋&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;컷셋(Cut Set)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;패스셋(Path Set)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;정의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나면&lt;/u&gt; 정상사상이 일어나는 집합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나지 않으면&lt;/u&gt; 정상사상이 일어나지 않는 집합&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;뜻&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템을 죽이는&lt;/u&gt; 조합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템을 살리는&lt;/u&gt; 조합&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;최소집합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소 컷셋 — 시스템의 위험도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소 패스셋 — 시스템의 신뢰성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;구하는 법&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Fussell Algorithm&lt;/u&gt; · &lt;u&gt;Limnios-Ziani(반복 사건이 많을 때)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;쌍대 FT 로 바꿔 최소 컷셋을 구한다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;고장이 발생하지 않도록 하는 집합&lt;/strong&gt;은 &lt;strong&gt;패스셋&lt;/strong&gt;이다. 최소 컷셋은 반대로 &lt;strong&gt;고장을 일으키는&lt;/strong&gt; 최소한의 집합이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;컷셋과 패스셋&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;컷셋(Cut Set)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;패스셋(Path Set)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;정의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나면&lt;/u&gt; 정상사상이 일어나는 집합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나지 않으면&lt;/u&gt; 정상사상이 일어나지 않는 집합&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;뜻&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템을 죽이는&lt;/u&gt; 조합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템을 살리는&lt;/u&gt; 조합&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;최소집합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소 컷셋 — 시스템의 위험도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소 패스셋 — 시스템의 신뢰성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;구하는 법&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Fussell Algorithm&lt;/u&gt; · &lt;u&gt;Limnios-Ziani(반복 사건이 많을 때)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;쌍대 FT로 바꿔 최소 컷셋을 구한다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
-          <t>① Fussell Algorithm 을 쓰는 것은 맞다.&lt;br&gt;② 정상사상을 일으키는 최소한의 집합이라는 것도 맞다.&lt;br&gt;③ 반복 사건이 많으면 Limnios-Ziani 알고리즘이 유리하다.</t>
+          <t>① Fussell Algorithm을 쓰는 것은 맞다.&lt;br&gt;② 정상사상을 일으키는 최소한의 집합이라는 것도 맞다.&lt;br&gt;③ 반복 사건이 많으면 Limnios-Ziani 알고리즘이 유리하다.</t>
         </is>
       </c>
       <c r="AI23" s="32" t="inlineStr">
@@ -4168,17 +4168,17 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OR 게이트&lt;/strong&gt;이므로 &lt;strong&gt;둘 다 일어나지 않을 확률을 1에서 뺀다&lt;/strong&gt;. $1 - ( 1 - 0.05 ) ( 1 - 0.03 ) = 1 - 0.95 \times 0.97 = 1 - 0.9215 = 0.0785$ 다.&lt;img src="safe_A_2025_01_022_exp1.png"&gt;&lt;em&gt;OR 게이트 — 하나만 일어나도 위가 일어난다&lt;/em&gt;</t>
+          <t>&lt;strong&gt;OR 게이트&lt;/strong&gt;이므로 &lt;strong&gt;둘 다 일어나지 않을 확률을 1에서 뺀다&lt;/strong&gt;. $1 - ( 1 - 0.05 ) ( 1 - 0.03 ) = 1 - 0.95 \times 0.97 = 1 - 0.9215 = 0.0785$다.&lt;img src="safe_A_2025_01_022_exp1.png"&gt;&lt;em&gt;OR 게이트 — 하나만 일어나도 위가 일어난다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
         <is>
-          <t>① 0.0015 는 AND 로 계산한 값 $0.05 \times 0.03$ 이다.&lt;br&gt;③ 0.9215 는 둘 다 일어나지 않을 확률이다.&lt;br&gt;④ 0.9985 는 1 에서 AND 값을 뺀 것이다.</t>
+          <t>① 0.0015는 AND로 계산한 값 $0.05 \times 0.03$이다.&lt;br&gt;③ 0.9215는 둘 다 일어나지 않을 확률이다.&lt;br&gt;④ 0.9985는 1에서 AND 값을 뺀 것이다.</t>
         </is>
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 논리 게이트의 확률 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;OR 는 &lt;/strong&gt;$1 - \prod ( 1 - q_{i} )$&lt;strong&gt;, AND 는 &lt;/strong&gt;$\prod q_{i}$다. 값이 작으면 OR 는 대략 &lt;strong&gt;확률의 합&lt;/strong&gt;에 가깝고, AND 는 &lt;strong&gt;훨씬 작아진다&lt;/strong&gt;. 여기서도 0.05+0.03=0.08 과 0.0785 가 거의 같다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;OR 는 1에서 빼고, AND 는 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA 논리 게이트의 확률 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;OR는 &lt;/strong&gt;$1 - \prod ( 1 - q_{i} )$&lt;strong&gt;, AND는 &lt;/strong&gt;$\prod q_{i}$다. 값이 작으면 OR는 대략 &lt;strong&gt;확률의 합&lt;/strong&gt;에 가깝고, AND는 &lt;strong&gt;훨씬 작아진다&lt;/strong&gt;. 여기서도 0.05+0.03=0.08과 0.0785가 거의 같다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;OR는 1에서 빼고, AND는 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4423,12 +4423,12 @@
       </c>
       <c r="AH26" s="32" t="inlineStr">
         <is>
-          <t>① 85 [dB] 는 강렬한 소음작업의 기준이 아니다.&lt;br&gt;② 85 [dB] 는 소음성 난청 건강진단의 기준 쪽이다.&lt;br&gt;③ 90 [dB] 에 4시간이라는 조합은 없다.</t>
+          <t>① 85 [dB]는 강렬한 소음작업의 기준이 아니다.&lt;br&gt;② 85 [dB]는 소음성 난청 건강진단의 기준 쪽이다.&lt;br&gt;③ 90 [dB]에 4시간이라는 조합은 없다.</t>
         </is>
       </c>
       <c r="AI26" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제512조 — 강렬한 소음작업&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;90 [dB] · 8시간&lt;/strong&gt;에서 시작해 &lt;strong&gt;5 [dB] 마다 시간이 절반&lt;/strong&gt;이다. &lt;strong&gt;충격소음작업&lt;/strong&gt;은 따로 정한다 — &lt;strong&gt;120 [dB] 초과 1만회 · 130 [dB] 초과 1천회 · 140 [dB] 초과 100회 이상&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;90 에 8시간, 5 오르면 반으로&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C512%EC%A1%B0" target="_blank"&gt;제512조(정의)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;이 장에서 사용하는 용어의 뜻은 다음과 같다. &amp;lt;개정 2024.6.28&amp;gt;&lt;br&gt;▶  1. "소음작업"이란 1일 &lt;strong&gt;8시간&lt;/strong&gt; 작업을 기준으로 85데시벨 이상의 소음이 발생하는 작업을 말한다.&lt;br&gt; 2. "강렬한 소음작업"이란 다음 각목의 어느 하나에 해당하는 작업을 말한다.&lt;br&gt;▶  가. &lt;strong&gt;90데시벨 이상의 소음이 1일 8시간 이상 발생하는 작업&lt;/strong&gt;&lt;br&gt; 나. 95데시벨 이상의 소음이 1일 4시간 이상 발생하는 작업&lt;br&gt; 다. 100데시벨 이상의 소음이 1일 2시간 이상 발생하는 작업&lt;br&gt; 라. 105데시벨 이상의 소음이 1일 1시간 이상 발생하는 작업&lt;br&gt; 마. 110데시벨 이상의 소음이 1일 30분 이상 발생하는 작업&lt;br&gt; 바. 115데시벨 이상의 소음이 1일 15분 이상 발생하는 작업&lt;br&gt;▶  3. "&lt;strong&gt;충격소음작업&lt;/strong&gt;"이란 소음이 1초 이상의 간격으로 발생하는 작업으로서 다음 각 목의 어느 하나에 해당하는 작업을 말한다.&lt;br&gt; 가. 120데시벨을 초과하는 소음이 1일 1만회 이상 발생하는 작업&lt;br&gt; 나. 130데시벨을 초과하는 소음이 1일 1천회 이상 발생하는 작업&lt;br&gt; 다. 140데시벨을 초과하는 소음이 1일 1백회 이상 발생하는 작업&lt;br&gt; 4. "진동작업"이란 다음 각 목의 어느 하나에 해당하는 기계ㆍ기구를 사용하는 작업을 말한다.&lt;br&gt; 가. 착암기(鑿巖機)&lt;br&gt; 나. 동력을 이용한 해머&lt;br&gt; 다. 체인톱&lt;br&gt; 라. 엔진 커터(engine cutter)&lt;br&gt; 마. 동력을 이용한 연삭기&lt;br&gt; 바. 임팩트 렌치(impact wrench)&lt;br&gt; 사. 그 밖에 진동으로 인하여 건강장해를 유발할 수 있는 기계ㆍ기구&lt;br&gt; 5. "청력보존 프로그램"이란 다음 각 목의 사항이 포함된 소음성 난청을 예방ㆍ관리하기 위한 종합적인 계획을 말한다.&lt;br&gt; 가. 소음노출 평가&lt;br&gt; 나. 소음노출에 대한 공학적 대책&lt;br&gt; 다. 청력보호구의 지급과 착용&lt;br&gt; 라. 소음의 유해성 및 예방 관련 교육&lt;br&gt; 마. 정기적 청력검사&lt;br&gt; 바. 청력보존 프로그램 수립 및 시행 관련 기록ㆍ관리체계&lt;br&gt; 사. 그 밖에 소음성 난청 예방ㆍ관리에 필요한 사항&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제512조 — 강렬한 소음작업&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;90 [dB] · 8시간&lt;/strong&gt;에서 시작해 &lt;strong&gt;5 [dB] 마다 시간이 절반&lt;/strong&gt;이다. &lt;strong&gt;충격소음작업&lt;/strong&gt;은 따로 정한다 — &lt;strong&gt;120 [dB] 초과 1만회 · 130 [dB] 초과 1천회 · 140 [dB] 초과 100회 이상&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;90에 8시간, 5 오르면 반으로&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C512%EC%A1%B0" target="_blank"&gt;제512조(정의)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;이 장에서 사용하는 용어의 뜻은 다음과 같다. &amp;lt;개정 2024.6.28&amp;gt;&lt;br&gt;▶  1. "소음작업"이란 1일 &lt;strong&gt;8시간&lt;/strong&gt; 작업을 기준으로 85데시벨 이상의 소음이 발생하는 작업을 말한다.&lt;br&gt; 2. "강렬한 소음작업"이란 다음 각목의 어느 하나에 해당하는 작업을 말한다.&lt;br&gt;▶  가. &lt;strong&gt;90데시벨 이상의 소음이 1일 8시간 이상 발생하는 작업&lt;/strong&gt;&lt;br&gt; 나. 95데시벨 이상의 소음이 1일 4시간 이상 발생하는 작업&lt;br&gt; 다. 100데시벨 이상의 소음이 1일 2시간 이상 발생하는 작업&lt;br&gt; 라. 105데시벨 이상의 소음이 1일 1시간 이상 발생하는 작업&lt;br&gt; 마. 110데시벨 이상의 소음이 1일 30분 이상 발생하는 작업&lt;br&gt; 바. 115데시벨 이상의 소음이 1일 15분 이상 발생하는 작업&lt;br&gt;▶  3. "&lt;strong&gt;충격소음작업&lt;/strong&gt;"이란 소음이 1초 이상의 간격으로 발생하는 작업으로서 다음 각 목의 어느 하나에 해당하는 작업을 말한다.&lt;br&gt; 가. 120데시벨을 초과하는 소음이 1일 1만회 이상 발생하는 작업&lt;br&gt; 나. 130데시벨을 초과하는 소음이 1일 1천회 이상 발생하는 작업&lt;br&gt; 다. 140데시벨을 초과하는 소음이 1일 1백회 이상 발생하는 작업&lt;br&gt; 4. "진동작업"이란 다음 각 목의 어느 하나에 해당하는 기계ㆍ기구를 사용하는 작업을 말한다.&lt;br&gt; 가. 착암기(鑿巖機)&lt;br&gt; 나. 동력을 이용한 해머&lt;br&gt; 다. 체인톱&lt;br&gt; 라. 엔진 커터(engine cutter)&lt;br&gt; 마. 동력을 이용한 연삭기&lt;br&gt; 바. 임팩트 렌치(impact wrench)&lt;br&gt; 사. 그 밖에 진동으로 인하여 건강장해를 유발할 수 있는 기계ㆍ기구&lt;br&gt; 5. "청력보존 프로그램"이란 다음 각 목의 사항이 포함된 소음성 난청을 예방ㆍ관리하기 위한 종합적인 계획을 말한다.&lt;br&gt; 가. 소음노출 평가&lt;br&gt; 나. 소음노출에 대한 공학적 대책&lt;br&gt; 다. 청력보호구의 지급과 착용&lt;br&gt; 라. 소음의 유해성 및 예방 관련 교육&lt;br&gt; 마. 정기적 청력검사&lt;br&gt; 바. 청력보존 프로그램 수립 및 시행 관련 기록ㆍ관리체계&lt;br&gt; 사. 그 밖에 소음성 난청 예방ㆍ관리에 필요한 사항&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① DT(Decision Tree)는 확률이 붙은 의사결정 전개도다.&lt;br&gt;② FTA 는 결과에서 원인으로 거슬러 올라가는 기법이다.&lt;br&gt;③ THERP 는 인간의 과오율을 예측하는 기법이다.</t>
+          <t>① DT(Decision Tree)는 확률이 붙은 의사결정 전개도다.&lt;br&gt;② FTA는 결과에서 원인으로 거슬러 올라가는 기법이다.&lt;br&gt;③ THERP는 인간의 과오율을 예측하는 기법이다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;MORT(Management Oversight and Risk Tree)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「원자력」·「관리까지 폭넓게」&lt;/strong&gt; 두 낱말이 나오면 MORT 다. &lt;strong&gt;「인간 과오율」이 나오면 THERP&lt;/strong&gt;다. 이 두 짝만 잡으면 이 유형은 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;원자력이면 MORT, 사람이면 THERP&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;MORT(Management Oversight and Risk Tree)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「원자력」·「관리까지 폭넓게」&lt;/strong&gt; 두 낱말이 나오면 MORT다. &lt;strong&gt;「인간 과오율」이 나오면 THERP&lt;/strong&gt;다. 이 두 짝만 잡으면 이 유형은 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;원자력이면 MORT, 사람이면 THERP&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="AG32" s="32" t="inlineStr">
         <is>
-          <t>가운데 세 갈래를 먼저 묶는다. 위·아래 갈래는 직렬이라 $0.8 \times 0.8 = 0.64$ 이고 가운데는 0.90 이다. 병렬이므로 $1 - ( 1 - 0.64 ) ( 1 - 0.90 ) ( 1 - 0.64 ) = 1 - 0.36 \times 0.10 \times 0.36 = 0.98704$ 다. 앞뒤 0.75 를 곱하면 $0.75 \times 0.98704 \times 0.75 \fallingdotseq 0.5552$ 다.&lt;img src="safe_A_2025_01_030_exp1.png"&gt;&lt;em&gt;세 갈래를 먼저 묶고, 앞뒤 직렬을 곱한다&lt;/em&gt;</t>
+          <t>가운데 세 갈래를 먼저 묶는다. 위·아래 갈래는 직렬이라 $0.8 \times 0.8 = 0.64$이고 가운데는 0.90이다. 병렬이므로 $1 - ( 1 - 0.64 ) ( 1 - 0.90 ) ( 1 - 0.64 ) = 1 - 0.36 \times 0.10 \times 0.36 = 0.98704$다. 앞뒤 0.75를 곱하면 $0.75 \times 0.98704 \times 0.75 \fallingdotseq 0.5552$다.&lt;img src="safe_A_2025_01_030_exp1.png"&gt;&lt;em&gt;세 갈래를 먼저 묶고, 앞뒤 직렬을 곱한다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH32" s="32" t="inlineStr">
         <is>
-          <t>② 0.5427 은 병렬 계산이 어긋난 값이다.&lt;br&gt;③ 0.6234 도 맞지 않는다.&lt;br&gt;④ 0.9740 은 앞뒤 0.75 를 빼먹은 값 쪽이다.</t>
+          <t>② 0.5427은 병렬 계산이 어긋난 값이다.&lt;br&gt;③ 0.6234 도 맞지 않는다.&lt;br&gt;④ 0.9740은 앞뒤 0.75를 빼먹은 값 쪽이다.</t>
         </is>
       </c>
       <c r="AI32" s="32" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="U33" s="32" t="inlineStr">
         <is>
-          <t>실린더 블록에 사용하는 가스켓의 수명은 평균 10000 시간이며, 표준편차는 200 시간으로 정규분포를 따른다. 사용시간이 9600 시간일 경우에 신뢰도는 약 얼마인가? (단, 표준정규분표표에서 u0.8413=1, u0.9772=2 이다.)</t>
+          <t>실린더 블록에 사용하는 가스켓의 수명은 평균 10000 시간이며, 표준편차는 200 시간으로 정규분포를 따른다. 사용시간이 9600 시간일 경우에 신뢰도는 약 얼마인가? (단, 표준정규분표표에서 u0.8413=1, u0.9772=2이다.)</t>
         </is>
       </c>
       <c r="V33" s="32" t="inlineStr"/>
@@ -5309,17 +5309,17 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>$Z = ( 9 {,} 600 - 10 {,} 000 ) / 200 =-2$ 다. 9,600시간을 &lt;strong&gt;넘겨 살아 있을 확률&lt;/strong&gt;이므로 $R = P ( Z &amp;gt; - 2 ) = P ( Z \le 2 ) = 0.9772$ 곧 &lt;strong&gt;97.72 [%]&lt;/strong&gt;다.</t>
+          <t>$Z = ( 9 {,} 600 - 10 {,} 000 ) / 200 =-2$다. 9,600시간을 &lt;strong&gt;넘겨 살아 있을 확률&lt;/strong&gt;이므로 $R = P ( Z &amp;gt; - 2 ) = P ( Z \le 2 ) = 0.9772$ 곧 &lt;strong&gt;97.72 [%]&lt;/strong&gt;다.</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① 84.13 [%] 는 $Z =-1$ 일 때다.&lt;br&gt;② 88.73 [%] 는 표에 없는 값이다.&lt;br&gt;③ 92.72 [%] 도 표에 없다.</t>
+          <t>① 84.13 [%]는 $Z =-1$일 때다.&lt;br&gt;② 88.73 [%]는 표에 없는 값이다.&lt;br&gt;③ 92.72 [%] 도 표에 없다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정규분포를 따르는 수명의 신뢰도&lt;/strong&gt;&lt;br&gt;$Z$ 가 음수로 나오면 &lt;strong&gt;정규분포가 좌우대칭&lt;/strong&gt;이므로 부호를 떼고 표를 그대로 읽는다. &lt;strong&gt;신뢰도는 「그 시각까지 버틸 확률」&lt;/strong&gt;이라 오른쪽 꼬리를 본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Z = ( t - \mu ) / \sigma$ — &lt;u&gt;음수면 대칭으로 뒤집는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정규분포를 따르는 수명의 신뢰도&lt;/strong&gt;&lt;br&gt;$Z$가 음수로 나오면 &lt;strong&gt;정규분포가 좌우대칭&lt;/strong&gt;이므로 부호를 떼고 표를 그대로 읽는다. &lt;strong&gt;신뢰도는 「그 시각까지 버틸 확률」&lt;/strong&gt;이라 오른쪽 꼬리를 본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Z = ( t - \mu ) / \sigma$ — &lt;u&gt;음수면 대칭으로 뒤집는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="AG37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;제4단계는 안전대책&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계 자료의 정비 검토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설계도 · 공정도 · 물질 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;입지 조건 · 배치 · 건조물 · 소방설비 · 원재료 · 공정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;취급물질 · 용량 · 온도 · 압력 · 조작 — A~D 등급&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설비 대책과 관리 대책&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;비슷한 사고 사례로 다시 본다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA 에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;등급 Ⅰ·Ⅱ 에 적용&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;제4단계는 안전대책&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계 자료의 정비 검토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설계도 · 공정도 · 물질 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;입지 조건 · 배치 · 건조물 · 소방설비 · 원재료 · 공정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;취급물질 · 용량 · 온도 · 압력 · 조작 — A~D 등급&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설비 대책과 관리 대책&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;비슷한 사고 사례로 다시 본다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;등급 Ⅰ·Ⅱ 에 적용&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH37" s="32" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AG38" s="32" t="inlineStr">
         <is>
-          <t>FTA 는 &lt;strong&gt;톱다운(Top-Down)&lt;/strong&gt; 방식이다. &lt;strong&gt;정상사상에서 시작해 아래로 원인을 캐 내려간다&lt;/strong&gt;. 바텀업은 FMEA 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 와 FMEA&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;FTA&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;FMEA&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;방향&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;위에서 아래로 (Top-Down)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아래에서 위로 (Bottom-Up)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;논리&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연역적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;귀납적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 가능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;잘하는 것&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여러 원인이 얽힌 재해&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부품 하나하나의 고장 영향&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;한계&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;숨은 원인을 빠뜨릴 수 있다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;여러 고장이 겹친 경우에 약하다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>FTA는 &lt;strong&gt;톱다운(Top-Down)&lt;/strong&gt; 방식이다. &lt;strong&gt;정상사상에서 시작해 아래로 원인을 캐 내려간다&lt;/strong&gt;. 바텀업은 FMEA다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA와 FMEA&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;FTA&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;FMEA&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;방향&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;위에서 아래로 (Top-Down)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아래에서 위로 (Bottom-Up)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;논리&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연역적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;귀납적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 가능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;잘하는 것&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여러 원인이 얽힌 재해&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부품 하나하나의 고장 영향&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;한계&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;숨은 원인을 빠뜨릴 수 있다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;여러 고장이 겹친 경우에 약하다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH38" s="32" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="AI38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 와 FMEA 의 대비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA 는 「왜 이 사고가 났나」를 위에서 파고, FMEA 는 「이 부품이 고장 나면 무슨 일이 나나」를 아래에서 쌓는다&lt;/strong&gt;. 방향이 정반대다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA 는 위에서 아래로, 연역·정량&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA와 FMEA의 대비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA는 「왜 이 사고가 났나」를 위에서 파고, FMEA는 「이 부품이 고장 나면 무슨 일이 나나」를 아래에서 쌓는다&lt;/strong&gt;. 방향이 정반대다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA는 위에서 아래로, 연역·정량&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="AG39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;C/R 비가 클수록 둔감&lt;/strong&gt; 하다. 조종장치를 많이 움직여야 표시장치가 조금 움직이기 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;C/R 비가 크면 어떻게 되나&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;C/R 비가 크다&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;C/R 비가 작다&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;민감도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둔감하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;민감하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;짧아진다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조정시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짧아진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;길어진다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;알맞은 일&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미세 조정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빠른 이동&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;C/R 비가 클수록 둔감&lt;/strong&gt;하다. 조종장치를 많이 움직여야 표시장치가 조금 움직이기 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;C/R 비가 크면 어떻게 되나&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;C/R 비가 크다&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;C/R 비가 작다&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;민감도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둔감하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;민감하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;짧아진다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조정시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짧아진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;길어진다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;알맞은 일&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미세 조정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빠른 이동&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH39" s="32" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;조종-반응비(C/R 비)&lt;/strong&gt;&lt;br&gt;$C / R = \dfrac{\text{조종장치의 이동거리}}{\text{표시장치의 이동거리}}$ 다. &lt;strong&gt;분자가 조종장치&lt;/strong&gt;이므로, 값이 크다는 것은 &lt;strong&gt;많이 돌려야 조금 움직인다&lt;/strong&gt;는 뜻이고 곧 둔감하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;C/R 이 크면 둔감&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;조종-반응비(C/R 비)&lt;/strong&gt;&lt;br&gt;$C / R = \dfrac{\text{조종장치의 이동거리}}{\text{표시장치의 이동거리}}$다. &lt;strong&gt;분자가 조종장치&lt;/strong&gt;이므로, 값이 크다는 것은 &lt;strong&gt;많이 돌려야 조금 움직인다&lt;/strong&gt;는 뜻이고 곧 둔감하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;C/R이 크면 둔감&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6341,17 @@
       </c>
       <c r="AG41" s="32" t="inlineStr">
         <is>
-          <t>확률은 파랑 0.5, 빨강 0.25, 노랑 0.25 다. $H = \sum p_{i} \log_{2} ( 1 / p_{i} )$ 이므로 $H = 0.5 \times 1 + 0.25 \times 2 + 0.25 \times 2 = 0.5 + 0.5 + 0.5 = 1.5$ [bit] 다.</t>
+          <t>확률은 파랑 0.5, 빨강 0.25, 노랑 0.25다. $H = \sum p_{i} \log_{2} ( 1 / p_{i} )$이므로 $H = 0.5 \times 1 + 0.25 \times 2 + 0.25 \times 2 = 0.5 + 0.5 + 0.5 = 1.5$ [bit]다.</t>
         </is>
       </c>
       <c r="AH41" s="32" t="inlineStr">
         <is>
-          <t>① 0.5 [bit] 는 파랑 몫만 센 값이다.&lt;br&gt;② 0.75 [bit] 도 계산과 맞지 않는다.&lt;br&gt;③ 1.0 [bit] 는 두 가지가 반반일 때의 값이다.</t>
+          <t>① 0.5 [bit]는 파랑 몫만 센 값이다.&lt;br&gt;② 0.75 [bit] 도 계산과 맞지 않는다.&lt;br&gt;③ 1.0 [bit]는 두 가지가 반반일 때의 값이다.</t>
         </is>
       </c>
       <c r="AI41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정보량과 엔트로피&lt;/strong&gt;&lt;br&gt;한 사건의 정보량은 $\log_{2} ( 1 / p )$ 이고, 전체 평균 정보량은 &lt;strong&gt;각 확률로 가중평균&lt;/strong&gt; 한다. &lt;strong&gt;확률이 모두 같을 때 정보량이 가장 크다&lt;/strong&gt; — 여기서 셋이 균등하면 $\log_{2} 3 = 1.585$ [bit] 가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = \sum p \log_{2} ( 1 / p )$ — &lt;u&gt;확률로 가중평균&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정보량과 엔트로피&lt;/strong&gt;&lt;br&gt;한 사건의 정보량은 $\log_{2} ( 1 / p )$이고, 전체 평균 정보량은 &lt;strong&gt;각 확률로 가중평균&lt;/strong&gt;한다. &lt;strong&gt;확률이 모두 같을 때 정보량이 가장 크다&lt;/strong&gt; — 여기서 셋이 균등하면 $\log_{2} 3 = 1.585$ [bit]가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = \sum p \log_{2} ( 1 / p )$ — &lt;u&gt;확률로 가중평균&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="AG43" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;12 [mm] 이내&lt;/strong&gt;다. 더 벌어지면 켠 자리가 다시 닫히며 &lt;strong&gt;톱날을 물어 반발&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;목재가공용 둥근톱의 방호장치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 막나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분할날(반발예방장치)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 원주면과 12 [mm] 이내&lt;/u&gt; · 두께는 톱날의 &lt;u&gt;1.1배 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;반발&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 후면 날의 2/3 이상&lt;/u&gt;을 덮을 것&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;톱날 접촉예방장치(덮개)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업 중 톱날이 드러나지 않게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;접촉&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;12 [mm] 이내&lt;/strong&gt;다. 더 벌어지면 켠 자리가 다시 닫히며 &lt;strong&gt;톱날을 물어 반발&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;목재가공용 둥근톱의 방호장치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 막나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분할날(반발예방장치)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 원주면과 12 [mm] 이내&lt;/u&gt; · 두께는 톱날의 &lt;u&gt;1.1배 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;반발&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 후면 날의 2/3 이상&lt;/u&gt;을 덮을 것&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;톱날 접촉예방장치(덮개)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업 중 톱날이 드러나지 않게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;접촉&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH43" s="32" t="inlineStr">
         <is>
-          <t>① 10 [mm] 는 기준보다 짧다.&lt;br&gt;③ 14 [mm] 는 기준을 넘는다.&lt;br&gt;④ 16 [mm] 도 기준을 넘는다.</t>
+          <t>① 10 [mm]는 기준보다 짧다.&lt;br&gt;③ 14 [mm]는 기준을 넘는다.&lt;br&gt;④ 16 [mm] 도 기준을 넘는다.</t>
         </is>
       </c>
       <c r="AI43" s="32" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="AG49" s="32" t="inlineStr">
         <is>
-          <t>$D_{m} = 1 {,} 600 \times T_{m}$ 이다. $1 {,} 600 \times 0.5 = 800$ [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;프레스 방호장치의 안전거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방호장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수기동식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D_{m} = 1 {,} 600 T_{m}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T_{m}$ 은 &lt;u&gt;하사점 도달시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{l} + T_{s} )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;급정지시간&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;광전자식(감응식)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{l} + T_{s} )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손쳐내기식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 0.5 \times \text{행정길이}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$D_{m} = 1 {,} 600 \times T_{m}$이다. $1 {,} 600 \times 0.5 = 800$ [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;프레스 방호장치의 안전거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방호장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수기동식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D_{m} = 1 {,} 600 T_{m}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T_{m}$은 &lt;u&gt;하사점 도달시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{l} + T_{s} )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;급정지시간&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;광전자식(감응식)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{l} + T_{s} )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손쳐내기식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 0.5 \times \text{행정길이}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH49" s="32" t="inlineStr">
         <is>
-          <t>① 200 [mm] 는 계수를 잘못 잡았을 때다.&lt;br&gt;② 400 [mm] 도 맞지 않는다.&lt;br&gt;③ 600 [mm] 도 맞지 않는다.</t>
+          <t>① 200 [mm]는 계수를 잘못 잡았을 때다.&lt;br&gt;② 400 [mm] 도 맞지 않는다.&lt;br&gt;③ 600 [mm] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI49" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;1,600 [mm/s] 는 &lt;strong&gt;사람 손이 움직이는 속도&lt;/strong&gt;로 잡은 값이다. &lt;strong&gt;손이 위험구역에 닿기 전에 슬라이드가 내려와 버리도록&lt;/strong&gt; 두 손 버튼을 그만큼 떨어뜨려 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,600 × 시간&lt;/u&gt; — 답은 [mm].&lt;/p&gt;</t>
+          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;1,600 [mm/s]는 &lt;strong&gt;사람 손이 움직이는 속도&lt;/strong&gt;로 잡은 값이다. &lt;strong&gt;손이 위험구역에 닿기 전에 슬라이드가 내려와 버리도록&lt;/strong&gt; 두 손 버튼을 그만큼 떨어뜨려 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,600 × 시간&lt;/u&gt; — 답은 [mm].&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="AH54" s="32" t="inlineStr">
         <is>
-          <t>① 50 [mm] 는 한 손으로도 누를 수 있다.&lt;br&gt;② 100 [mm] 도 마찬가지다.&lt;br&gt;③ 200 [mm] 도 기준에 못 미친다.</t>
+          <t>① 50 [mm]는 한 손으로도 누를 수 있다.&lt;br&gt;② 100 [mm] 도 마찬가지다.&lt;br&gt;③ 200 [mm] 도 기준에 못 미친다.</t>
         </is>
       </c>
       <c r="AI54" s="32" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>주행 시 좌우 안정도는 $( 15 + 1.1 V )$ [%] 다. $15 + 1.1 \times 20 = 15 + 22 = 37$ [%] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5톤 이상은 &lt;u&gt;3.5 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V) [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;V 는 [km/h]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_01_057_exp1.png"&gt;&lt;em&gt;지게차 안정도 — 하역은 작고 주행은 크다&lt;/em&gt;</t>
+          <t>주행 시 좌우 안정도는 $( 15 + 1.1 V )$ [%]다. $15 + 1.1 \times 20 = 15 + 22 = 37$ [%]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5톤 이상은 &lt;u&gt;3.5 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V) [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;V는 [km/h]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_01_057_exp1.png"&gt;&lt;em&gt;지게차 안정도 — 하역은 작고 주행은 크다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>② 39 [%] 는 계수를 잘못 잡았을 때다.&lt;br&gt;③ 41 [%] 도 맞지 않는다.&lt;br&gt;④ 43 [%] 도 맞지 않는다.</t>
+          <t>② 39 [%]는 계수를 잘못 잡았을 때다.&lt;br&gt;③ 41 [%] 도 맞지 않는다.&lt;br&gt;④ 43 [%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="AG60" s="32" t="inlineStr">
         <is>
-          <t>$W = m ( g + a ) = 100 \times ( 9.8 + 5 ) = 100 \times 14.8 = 1 {,} 480$ [N] 이다.</t>
+          <t>$W = m ( g + a ) = 100 \times ( 9.8 + 5 ) = 100 \times 14.8 = 1 {,} 480$ [N]이다.</t>
         </is>
       </c>
       <c r="AH60" s="32" t="inlineStr">
         <is>
-          <t>① 500 [N] 은 동하중만 구한 값이다.&lt;br&gt;③ 2,540 [N] 은 계산과 맞지 않는다.&lt;br&gt;④ 4,900 [N] 은 정하중만 구한 값 $100 \times 9.8$ 이다.</t>
+          <t>① 500 [N]은 동하중만 구한 값이다.&lt;br&gt;③ 2,540 [N]은 계산과 맞지 않는다.&lt;br&gt;④ 4,900 [N]은 정하중만 구한 값 $100 \times 9.8$이다.</t>
         </is>
       </c>
       <c r="AI60" s="32" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AH61" s="32" t="inlineStr">
         <is>
-          <t>① 와이어로프 1 [mm] 는 너무 가늘다.&lt;br&gt;② 합성섬유로프는 2 [mm] 가 아니라 6 [mm] 이상이다.&lt;br&gt;③ 합성섬유로프 3 [mm] 도 기준에 못 미친다.</t>
+          <t>① 와이어로프 1 [mm]는 너무 가늘다.&lt;br&gt;② 합성섬유로프는 2 [mm]가 아니라 6 [mm] 이상이다.&lt;br&gt;③ 합성섬유로프 3 [mm] 도 기준에 못 미친다.</t>
         </is>
       </c>
       <c r="AI61" s="32" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="AG64" s="32" t="inlineStr">
         <is>
-          <t>접지는 &lt;strong&gt;대지전위 상승을 억제&lt;/strong&gt; 하는 것까지는 맞지만, &lt;strong&gt;절연강도를 「낮춰도 되게」&lt;/strong&gt; 해 주는 것이지 &lt;strong&gt;올려 주는 것이 아니다&lt;/strong&gt;.</t>
+          <t>접지는 &lt;strong&gt;대지전위 상승을 억제&lt;/strong&gt;하는 것까지는 맞지만, &lt;strong&gt;절연강도를 「낮춰도 되게」&lt;/strong&gt;해 주는 것이지 &lt;strong&gt;올려 주는 것이 아니다&lt;/strong&gt;.</t>
         </is>
       </c>
       <c r="AH64" s="32" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AG65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;통전경로&lt;/strong&gt;는 &lt;strong&gt;전류가 어디로 흐르는가&lt;/strong&gt;를 말할 뿐, &lt;strong&gt;피부 저항 자체를 바꾸지는 않는다&lt;/strong&gt;. 위험도에는 영향을 주지만 저항의 인자는 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;피부 전기저항에 영향을 주는 것&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인자&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접촉면적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;넓을수록 저항이 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전류가 지날 길이 넓어진다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인가전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높을수록 저항이 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;각질층이 뚫린다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인가시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길수록 저항이 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;땀이 나고 각질이 젖는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접촉부위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부위마다 다르다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;손바닥·발바닥은 두껍다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수분(땀)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;젖을수록 저항이 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1/12 ~ 1/25 로 떨어진다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;통전경로&lt;/strong&gt;는 &lt;strong&gt;전류가 어디로 흐르는가&lt;/strong&gt;를 말할 뿐, &lt;strong&gt;피부 저항 자체를 바꾸지는 않는다&lt;/strong&gt;. 위험도에는 영향을 주지만 저항의 인자는 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;피부 전기저항에 영향을 주는 것&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인자&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접촉면적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;넓을수록 저항이 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전류가 지날 길이 넓어진다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인가전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높을수록 저항이 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;각질층이 뚫린다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인가시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길수록 저항이 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;땀이 나고 각질이 젖는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접촉부위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부위마다 다르다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;손바닥·발바닥은 두껍다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수분(땀)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;젖을수록 저항이 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1/12 ~ 1/25로 떨어진다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH65" s="32" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="AI65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인체의 전기저항&lt;/strong&gt;&lt;br&gt;인체 저항의 어림값 — &lt;strong&gt;피부 저항 약 2,500 [Ω], 내부 저항 약 500 [Ω]&lt;/strong&gt;. &lt;strong&gt;젖으면 1/25 까지&lt;/strong&gt; 떨어져 같은 전압에서도 훨씬 위험해진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;통전경로는 위험도를 가르지 저항을 바꾸지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인체의 전기저항&lt;/strong&gt;&lt;br&gt;인체 저항의 어림값 — &lt;strong&gt;피부 저항 약 2,500 [Ω], 내부 저항 약 500 [Ω]&lt;/strong&gt;. &lt;strong&gt;젖으면 1/25까지&lt;/strong&gt; 떨어져 같은 전압에서도 훨씬 위험해진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;통전경로는 위험도를 가르지 저항을 바꾸지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9571,12 +9571,12 @@
       </c>
       <c r="AH66" s="32" t="inlineStr">
         <is>
-          <t>① 10 [mA] 라는 기준은 없다.&lt;br&gt;② 20 [mA] · 0.01초라는 기준도 없다.&lt;br&gt;④ 50 [mA] 는 심실세동 위험 영역이다.</t>
+          <t>① 10 [mA]라는 기준은 없다.&lt;br&gt;② 20 [mA] · 0.01초라는 기준도 없다.&lt;br&gt;④ 50 [mA]는 심실세동 위험 영역이다.</t>
         </is>
       </c>
       <c r="AI66" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;한국전기설비규정(KEC) 211.2.4 — 누전차단기의 시설&lt;/strong&gt;&lt;br&gt;Dalziel 의 심실세동전류 $I = 165 / \sqrt{T}$ [mA] 에서, $T = 0.03$ 초일 때 약 &lt;strong&gt;953 [mA]&lt;/strong&gt;까지 견딘다. &lt;strong&gt;30 [mA] 는 그보다 훨씬 낮게 잡은 여유값&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;일반 30, 물기 15 — 시간은 둘 다 0.03초&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;한국전기설비규정(KEC) 211.2.4 — 누전차단기의 시설&lt;/strong&gt;&lt;br&gt;Dalziel의 심실세동전류 $I = 165 / \sqrt{T}$ [mA]에서, $T = 0.03$ 초일 때 약 &lt;strong&gt;953 [mA]&lt;/strong&gt;까지 견딘다. &lt;strong&gt;30 [mA]는 그보다 훨씬 낮게 잡은 여유값&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;일반 30, 물기 15 — 시간은 둘 다 0.03초&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AI68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;교류 아크 용접기의 자동전격방지장치&lt;/strong&gt;&lt;br&gt;교류 아크 용접기의 무부하 전압은 &lt;strong&gt;60~95 [V]&lt;/strong&gt;로 감전 위험이 크다. 그래서 &lt;strong&gt;쉬는 동안만 전압을 낮춰 두었다가, 용접봉이 모재에 닿는 순간 정상 전압을 공급&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;쉴 때 끊고, 용접할 때 붙인다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;교류 아크 용접기의 자동전격방지장치&lt;/strong&gt;&lt;br&gt;교류 아크 용접기의 무부하 전압은 &lt;strong&gt;60~95 [V]&lt;/strong&gt;로 감전 위험이 크다. 그래서 &lt;strong&gt;쉬는 동안만 전압을 낮춰 두었다가, 용접봉이 모재에 닿는 순간 정상 전압을 공급&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;쉴 때 끊고, 용접할 때 붙인다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9953,17 +9953,17 @@
       </c>
       <c r="AG69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;300 [cm] 이내로 접근할 수 없다&lt;/strong&gt;. 50 [kV] 까지는 &lt;strong&gt;300 [cm]&lt;/strong&gt;이고, &lt;strong&gt;50 [kV] 를 넘으면 10 [kV] 마다 10 [cm] 씩 더&lt;/strong&gt; 띄운다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;유자격자가 아닌 근로자의 접근 한계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대지전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접근 한계거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 [kV] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [cm] + 10 [kV] 마다 10 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;300 [cm] 이내로 접근할 수 없다&lt;/strong&gt;. 50 [kV] 까지는 &lt;strong&gt;300 [cm]&lt;/strong&gt;이고, &lt;strong&gt;50 [kV]를 넘으면 10 [kV] 마다 10 [cm] 씩 더&lt;/strong&gt; 띄운다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;유자격자가 아닌 근로자의 접근 한계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대지전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접근 한계거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 [kV] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [cm] + 10 [kV] 마다 10 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH69" s="32" t="inlineStr">
         <is>
-          <t>① 50 [cm] 는 기준에 크게 못 미친다.&lt;br&gt;② 100 [cm] 도 못 미친다.&lt;br&gt;③ 200 [cm] 도 못 미친다.</t>
+          <t>① 50 [cm]는 기준에 크게 못 미친다.&lt;br&gt;② 100 [cm] 도 못 미친다.&lt;br&gt;③ 200 [cm] 도 못 미친다.</t>
         </is>
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제321조 — 충전전로 인근에서의 작업&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;차량이나 기계장치&lt;/strong&gt;는 따로 정한다 — &lt;strong&gt;충전전로에서 10 [m] 이상 이격&lt;/strong&gt;, 대지전압 50 [kV] 초과 시 &lt;strong&gt;10 [kV] 마다 10 [cm] 씩 추가&lt;/strong&gt;. 사람은 3 [m], 장비는 10 [m] 다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사람 300 [cm], 장비 10 [m]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C321%EC%A1%B0" target="_blank"&gt;제321조(충전전로에서의 전기작업)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 근로자가 충전전로를 취급하거나 그 인근에서 작업하는 경우에는 다음 각 호의 조치를 하여야 한다.&lt;br&gt; 1. 충전전로를 정전시키는 경우에는 제319조에 따른 조치를 할 것&lt;br&gt; 2. 충전전로를 방호, 차폐하거나 절연 등의 조치를 하는 경우에는 근로자의 신체가 전로와 직접 접촉하거나 도전재료, 공구 또는 기기를 통하여 간접 접촉되지 않도록 할 것&lt;br&gt; 3. 충전전로를 취급하는 근로자에게 그 작업에 적합한 절연용 보호구를 착용시킬 것&lt;br&gt; 4. 충전전로에 근접한 장소에서 전기작업을 하는 경우에는 해당 전압에 적합한 절연용 방호구를 설치할 것. 다만, 저압인 경우에는 해당 전기작업자가 절연용 보호구를 착용하되, 충전전로에 접촉할 우려가 없는 경우에는 절연용 방호구를 설치하지 아니할 수 있다.&lt;br&gt; 5. 고압 및 특별고압의 전로에서 전기작업을 하는 근로자에게 활선작업용 기구 및 장치를 사용하도록 할 것&lt;br&gt; 6. 근로자가 절연용 방호구의 설치ㆍ해체작업을 하는 경우에는 절연용 보호구를 착용하거나 활선작업용 기구 및 장치를 사용하도록 할 것&lt;br&gt;▶  7. 유자격자가 아닌 근로자가 충전전로 인근의 높은 곳에서 작업할 때에 근로자의 몸 또는 긴 도전성 물체가 방호되지 않은 충전전로에서 대지전압이 50킬로볼트 이하인 경우에는 300센티미터 이내로, 대지전압이 50킬로볼트를 넘는 경우에는 10킬로볼트당 10센티미터씩 더한 거리 이내로 각각 접근할 수 없도록 할 것&lt;br&gt; 8. 유자격자가 충전전로 인근에서 작업하는 경우에는 다음 각 목의 경우를 제외하고는 노출 충전부에 다음 표에 제시된 접근한계거리 이내로 접근하거나 절연 손잡이가 없는 도전체에 접근할 수 없도록 할 것&lt;br&gt; 가. 근로자가 노출 충전부로부터 절연된 경우 또는 해당 전압에 적합한 절연장갑을 착용한 경우&lt;br&gt; 나. 노출 충전부가 다른 전위를 갖는 도전체 또는 근로자와 절연된 경우&lt;br&gt; 다. 근로자가 다른 전위를 갖는 모든 도전체로부터 절연된 경우&lt;br&gt;&amp;lt;img src="http://www.law.go.kr/flDownload.do?flSeq=23019731" alt="img23019731" &amp;gt;&lt;br&gt;┌──────────┬────────┐&lt;br&gt;│충전전로의 선간전압 │충전전로에 대한 │&lt;br&gt;│(단위: 킬로볼트) │접근 한계거리 │&lt;br&gt;│ │(단위: 센티미터)│&lt;br&gt;├──────────┼────────┤&lt;br&gt;│0.3 이하 │접촉금지 │&lt;br&gt;│0.3 초과 0.75 이하 │30 │&lt;br&gt;│0.75 초과 2 이하 │45 │&lt;br&gt;│2 초과 15 이하 │60 │&lt;br&gt;│15 초과 37 이하 │90 │&lt;br&gt;│37 초과 88 이하 │110 │&lt;br&gt;│88 초과 121 이하 │130 │&lt;br&gt;│121 초과 145 이하 │150 │&lt;br&gt;│145 초과 169 이하 │170 │&lt;br&gt;│169 초과 242 이하 │230 │&lt;br&gt;│242 초과 362 이하 │380 │&lt;br&gt;│362 초과 550 이하 │550 │&lt;br&gt;│550 초과 800 이하 │790 │&lt;br&gt;└──────────┴────────┘&lt;br&gt;&amp;lt;/img&amp;gt;&lt;br&gt;② 사업주는 절연이 되지 않은 충전부나 그 인근에 근로자가 접근하는 것을 막거나 제한할 필요가 있는 경우에는 울타리를 설치하고 근로자가 쉽게 알아볼 수 있도록 하여야 한다. 다만, 전기와 접촉할 위험이 있는 경우에는 도전성이 있는 금속제 울타리를 사용하거나, 제1항의 표에 정한 접근 한계거리 이내에 설치해서는 아니 된다. &amp;lt;개정 2019.10.15&amp;gt;&lt;br&gt;③ 사업주는 제2항의 조치가 곤란한 경우에는 근로자를 감전위험에서 보호하기 위하여 사전에 위험을 경고하는 감시인을 배치하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제321조 — 충전전로 인근에서의 작업&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;차량이나 기계장치&lt;/strong&gt;는 따로 정한다 — &lt;strong&gt;충전전로에서 10 [m] 이상 이격&lt;/strong&gt;, 대지전압 50 [kV] 초과 시 &lt;strong&gt;10 [kV] 마다 10 [cm] 씩 추가&lt;/strong&gt;. 사람은 3 [m], 장비는 10 [m]다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사람 300 [cm], 장비 10 [m]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C321%EC%A1%B0" target="_blank"&gt;제321조(충전전로에서의 전기작업)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 근로자가 충전전로를 취급하거나 그 인근에서 작업하는 경우에는 다음 각 호의 조치를 하여야 한다.&lt;br&gt; 1. 충전전로를 정전시키는 경우에는 제319조에 따른 조치를 할 것&lt;br&gt; 2. 충전전로를 방호, 차폐하거나 절연 등의 조치를 하는 경우에는 근로자의 신체가 전로와 직접 접촉하거나 도전재료, 공구 또는 기기를 통하여 간접 접촉되지 않도록 할 것&lt;br&gt; 3. 충전전로를 취급하는 근로자에게 그 작업에 적합한 절연용 보호구를 착용시킬 것&lt;br&gt; 4. 충전전로에 근접한 장소에서 전기작업을 하는 경우에는 해당 전압에 적합한 절연용 방호구를 설치할 것. 다만, 저압인 경우에는 해당 전기작업자가 절연용 보호구를 착용하되, 충전전로에 접촉할 우려가 없는 경우에는 절연용 방호구를 설치하지 아니할 수 있다.&lt;br&gt; 5. 고압 및 특별고압의 전로에서 전기작업을 하는 근로자에게 활선작업용 기구 및 장치를 사용하도록 할 것&lt;br&gt; 6. 근로자가 절연용 방호구의 설치ㆍ해체작업을 하는 경우에는 절연용 보호구를 착용하거나 활선작업용 기구 및 장치를 사용하도록 할 것&lt;br&gt;▶  7. 유자격자가 아닌 근로자가 충전전로 인근의 높은 곳에서 작업할 때에 근로자의 몸 또는 긴 도전성 물체가 방호되지 않은 충전전로에서 대지전압이 50킬로볼트 이하인 경우에는 300센티미터 이내로, 대지전압이 50킬로볼트를 넘는 경우에는 10킬로볼트당 10센티미터씩 더한 거리 이내로 각각 접근할 수 없도록 할 것&lt;br&gt; 8. 유자격자가 충전전로 인근에서 작업하는 경우에는 다음 각 목의 경우를 제외하고는 노출 충전부에 다음 표에 제시된 접근한계거리 이내로 접근하거나 절연 손잡이가 없는 도전체에 접근할 수 없도록 할 것&lt;br&gt; 가. 근로자가 노출 충전부로부터 절연된 경우 또는 해당 전압에 적합한 절연장갑을 착용한 경우&lt;br&gt; 나. 노출 충전부가 다른 전위를 갖는 도전체 또는 근로자와 절연된 경우&lt;br&gt; 다. 근로자가 다른 전위를 갖는 모든 도전체로부터 절연된 경우&lt;br&gt;&amp;lt;img src="http://www.law.go.kr/flDownload.do?flSeq=23019731" alt="img23019731" &amp;gt;&lt;br&gt;┌──────────┬────────┐&lt;br&gt;│충전전로의 선간전압 │충전전로에 대한 │&lt;br&gt;│(단위: 킬로볼트) │접근 한계거리 │&lt;br&gt;│ │(단위: 센티미터)│&lt;br&gt;├──────────┼────────┤&lt;br&gt;│0.3 이하 │접촉금지 │&lt;br&gt;│0.3 초과 0.75 이하 │30 │&lt;br&gt;│0.75 초과 2 이하 │45 │&lt;br&gt;│2 초과 15 이하 │60 │&lt;br&gt;│15 초과 37 이하 │90 │&lt;br&gt;│37 초과 88 이하 │110 │&lt;br&gt;│88 초과 121 이하 │130 │&lt;br&gt;│121 초과 145 이하 │150 │&lt;br&gt;│145 초과 169 이하 │170 │&lt;br&gt;│169 초과 242 이하 │230 │&lt;br&gt;│242 초과 362 이하 │380 │&lt;br&gt;│362 초과 550 이하 │550 │&lt;br&gt;│550 초과 800 이하 │790 │&lt;br&gt;└──────────┴────────┘&lt;br&gt;&amp;lt;/img&amp;gt;&lt;br&gt;② 사업주는 절연이 되지 않은 충전부나 그 인근에 근로자가 접근하는 것을 막거나 제한할 필요가 있는 경우에는 울타리를 설치하고 근로자가 쉽게 알아볼 수 있도록 하여야 한다. 다만, 전기와 접촉할 위험이 있는 경우에는 도전성이 있는 금속제 울타리를 사용하거나, 제1항의 표에 정한 접근 한계거리 이내에 설치해서는 아니 된다. &amp;lt;개정 2019.10.15&amp;gt;&lt;br&gt;③ 사업주는 제2항의 조치가 곤란한 경우에는 근로자를 감전위험에서 보호하기 위하여 사전에 위험을 경고하는 감시인을 배치하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="AG70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1.2 [μs] 는 파두장, 50 [μs] 는 파미장&lt;/strong&gt;이다. 파두장은 &lt;strong&gt;꼭짓값까지 오르는 시간&lt;/strong&gt;, 파미장은 &lt;strong&gt;꼭짓값의 절반으로 떨어질 때까지의 시간&lt;/strong&gt;이다.</t>
+          <t>&lt;strong&gt;1.2 [μs]는 파두장, 50 [μs]는 파미장&lt;/strong&gt;이다. 파두장은 &lt;strong&gt;꼭짓값까지 오르는 시간&lt;/strong&gt;, 파미장은 &lt;strong&gt;꼭짓값의 절반으로 떨어질 때까지의 시간&lt;/strong&gt;이다.</t>
         </is>
       </c>
       <c r="AH70" s="32" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="AI72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;내압(耐壓) 방폭구조 d 와 최대안전틈새&lt;/strong&gt;&lt;br&gt;이 틈이 &lt;strong&gt;화염일주한계(최대안전틈새)&lt;/strong&gt;이고, 그 값으로 &lt;strong&gt;기기그룹 ⅡA · ⅡB · ⅡC&lt;/strong&gt;를 나눈다. &lt;strong&gt;틈이 좁아야 하는 가스일수록 위험&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;좁은 틈을 지나며 화염이 식는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;내압(耐壓) 방폭구조 d와 최대안전틈새&lt;/strong&gt;&lt;br&gt;이 틈이 &lt;strong&gt;화염일주한계(최대안전틈새)&lt;/strong&gt;이고, 그 값으로 &lt;strong&gt;기기그룹 ⅡA · ⅡB · ⅡC&lt;/strong&gt;를 나눈다. &lt;strong&gt;틈이 좁아야 하는 가스일수록 위험&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;좁은 틈을 지나며 화염이 식는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10590,17 +10590,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$V = \sqrt{2 W / C}$ 다. $V = \sqrt{2 \times 0.26 \times 10^{-3} / ( 100 \times 10^{-12} )} = \sqrt{5.2 \times 10^{6}} \fallingdotseq 2 {,} 280$ [V] 다.</t>
+          <t>$V = \sqrt{2 W / C}$다. $V = \sqrt{2 \times 0.26 \times 10^{-3} / ( 100 \times 10^{-12} )} = \sqrt{5.2 \times 10^{6}} \fallingdotseq 2 {,} 280$ [V]다.</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① 2,240 [V] 는 계산과 조금 어긋난다.&lt;br&gt;② 2,260 [V] 도 어긋난다.&lt;br&gt;④ 2,300 [V] 도 어긋난다.</t>
+          <t>① 2,240 [V]는 계산과 조금 어긋난다.&lt;br&gt;② 2,260 [V] 도 어긋난다.&lt;br&gt;④ 2,300 [V] 도 어긋난다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기 에너지와 착화한계전압&lt;/strong&gt;&lt;br&gt;$W = \dfrac{1}{2} C V^{2}$ 을 $V$ 에 대해 푼 식이다. &lt;strong&gt;[mJ] 는 &lt;/strong&gt;$10^{-3}$&lt;strong&gt;, [pF] 는 &lt;/strong&gt;$10^{-12}$로 바꾸는 자리에서 자릿수를 놓치기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \sqrt{2 W / C}$ — &lt;u&gt;단위를 [J] 와 [F] 로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기 에너지와 착화한계전압&lt;/strong&gt;&lt;br&gt;$W = \dfrac{1}{2} C V^{2}$을 $V$에 대해 푼 식이다. &lt;strong&gt;[mJ]는 &lt;/strong&gt;$10^{-3}$&lt;strong&gt;, [pF]는 &lt;/strong&gt;$10^{-12}$로 바꾸는 자리에서 자릿수를 놓치기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \sqrt{2 W / C}$ — &lt;u&gt;단위를 [J]와 [F]로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10724,12 +10724,12 @@
       </c>
       <c r="AH75" s="32" t="inlineStr">
         <is>
-          <t>① 600 [mA] 는 1/500 로 잡았을 때다.&lt;br&gt;② 450 [mA] 도 계산과 맞지 않는다.&lt;br&gt;③ 300 [mA] 는 1/1,000 로 잡았을 때다.</t>
+          <t>① 600 [mA]는 1/500로 잡았을 때다.&lt;br&gt;② 450 [mA] 도 계산과 맞지 않는다.&lt;br&gt;③ 300 [mA]는 1/1,000로 잡았을 때다.</t>
         </is>
       </c>
       <c r="AI75" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;저압 전선로의 누설전류 한도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1/2,000 이하&lt;/strong&gt;라는 이 조건에서 &lt;strong&gt;절연저항의 최솟값&lt;/strong&gt;도 나온다. 옴의 법칙으로 되돌리면 $R = \text{전압} \div \text{누설전류}$ 다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설은 최대공급전류의 1/2,000&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;저압 전선로의 누설전류 한도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1/2,000 이하&lt;/strong&gt;라는 이 조건에서 &lt;strong&gt;절연저항의 최솟값&lt;/strong&gt;도 나온다. 옴의 법칙으로 되돌리면 $R = \text{전압} \div \text{누설전류}$다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설은 최대공급전류의 1/2,000&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="AG76" s="32" t="inlineStr">
         <is>
-          <t>순서가 거꾸로다. &lt;strong&gt;전원을 먼저 차단한 뒤 단로기를 개방&lt;/strong&gt; 한다. 부하가 걸린 채 단로기를 열면 &lt;strong&gt;아크가 크게 튀어&lt;/strong&gt; 화상과 화재로 이어진다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전작업의 절차 (규칙 제319조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 전원을 도면·배선도로 확인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;빠뜨린 전원이 없게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원을 차단&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차단기로 먼저 끊는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;각 단로기를 개방하고 확인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부하 차단 뒤에 연다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잠금장치와 꼬리표 부착&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;남이 못 넣게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;⑤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잔류전하 방전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;콘덴서·케이블&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;⑥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;검전기로 충전 여부 확인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;눈으로 믿지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;⑦&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단락 접지기구로 단락 접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;그래도 들어올 경우를 대비&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>순서가 거꾸로다. &lt;strong&gt;전원을 먼저 차단한 뒤 단로기를 개방&lt;/strong&gt;한다. 부하가 걸린 채 단로기를 열면 &lt;strong&gt;아크가 크게 튀어&lt;/strong&gt; 화상과 화재로 이어진다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전작업의 절차 (규칙 제319조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 전원을 도면·배선도로 확인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;빠뜨린 전원이 없게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원을 차단&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차단기로 먼저 끊는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;각 단로기를 개방하고 확인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부하 차단 뒤에 연다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잠금장치와 꼬리표 부착&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;남이 못 넣게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;⑤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잔류전하 방전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;콘덴서·케이블&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;⑥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;검전기로 충전 여부 확인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;눈으로 믿지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;⑦&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단락 접지기구로 단락 접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;그래도 들어올 경우를 대비&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH76" s="32" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="AH77" s="32" t="inlineStr">
         <is>
-          <t>① 80 [℃] 인 종별은 없다.&lt;br&gt;② 85 [℃] 인 종별도 없다.&lt;br&gt;④ 105 [℃] 는 A종이다.</t>
+          <t>① 80 [℃] 인 종별은 없다.&lt;br&gt;② 85 [℃] 인 종별도 없다.&lt;br&gt;④ 105 [℃]는 A종이다.</t>
         </is>
       </c>
       <c r="AI77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전기기기 절연물의 종별&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Y 90 → A 105 → E 120 → B 130 → F 155 → H 180 → C 180 초과&lt;/strong&gt;로 올라간다. &lt;strong&gt;Y·A·E 는 15 [℃] 씩, B 부터는 25 [℃] 씩&lt;/strong&gt; 벌어진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Y 90 · A 105 · E 120 · B 130 · F 155 · H 180&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전기기기 절연물의 종별&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Y 90 → A 105 → E 120 → B 130 → F 155 → H 180 → C 180 초과&lt;/strong&gt;로 올라간다. &lt;strong&gt;Y·A·E는 15 [℃] 씩, B 부터는 25 [℃] 씩&lt;/strong&gt; 벌어진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Y 90 · A 105 · E 120 · B 130 · F 155 · H 180&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="AG79" s="32" t="inlineStr">
         <is>
-          <t>송전할 때는 잠금장치와 꼬리표를 &lt;strong&gt;설치하는 것이 아니라 제거&lt;/strong&gt; 한다. 설치는 &lt;strong&gt;정전할 때&lt;/strong&gt; 하는 일이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전 뒤 다시 전원을 넣을 때의 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업기구와 단락 접지기구를 제거&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;남아 있으면 단락된다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통전될 수 있는지 확인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 작업자가 떨어져 있는지 확인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사람이 먼저다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잠금장치와 꼬리표를 제거&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설치가 아니라 제거&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;⑤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원을 투입&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>송전할 때는 잠금장치와 꼬리표를 &lt;strong&gt;설치하는 것이 아니라 제거&lt;/strong&gt;한다. 설치는 &lt;strong&gt;정전할 때&lt;/strong&gt;하는 일이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전 뒤 다시 전원을 넣을 때의 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업기구와 단락 접지기구를 제거&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;남아 있으면 단락된다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통전될 수 있는지 확인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 작업자가 떨어져 있는지 확인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사람이 먼저다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잠금장치와 꼬리표를 제거&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설치가 아니라 제거&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;⑤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원을 투입&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH79" s="32" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="AI79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제319조 — 정전작업 후의 조치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정전할 때 붙인 것을 송전할 때 떼어 낸다&lt;/strong&gt;는 대칭 구조다. 잠금장치와 꼬리표는 &lt;strong&gt;설치한 사람이 직접 제거&lt;/strong&gt; 하는 것이 원칙이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;송전할 때는 붙이는 게 아니라 떼어 낸다&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C319%EC%A1%B0" target="_blank"&gt;제319조(정전전로에서의 전기작업)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 근로자가 노출된 충전부 또는 그 부근에서 작업함으로써 감전될 우려가 있는 경우에는 작업에 들어가기 전에 해당 전로를 차단하여야 한다. 다만, 다음 각 호의 경우에는 그러하지 아니하다.&lt;br&gt; 1. 생명유지장치, 비상경보설비, 폭발위험장소의 환기설비, 비상조명설비 등의 장치ㆍ설비의 가동이 중지되어 사고의 위험이 증가되는 경우&lt;br&gt; 2. 기기의 설계상 또는 작동상 제한으로 전로차단이 불가능한 경우&lt;br&gt; 3. 감전, 아크 등으로 인한 화상, 화재ㆍ폭발의 위험이 없는 것으로 확인된 경우&lt;br&gt;② 제1항의 전로 차단은 다음 각 호의 절차에 따라 시행하여야 한다.&lt;br&gt; 1. 전기기기등에 공급되는 모든 전원을 관련 도면, 배선도 등으로 확인할 것&lt;br&gt; 2. 전원을 차단한 후 각 단로기 등을 개방하고 확인할 것&lt;br&gt; 3. 차단장치나 단로기 등에 잠금장치 및 꼬리표를 부착할 것&lt;br&gt; 4. 개로된 전로에서 유도전압 또는 전기에너지가 축적되어 근로자에게 전기위험을 끼칠 수 있는 전기기기등은 접촉하기 전에 잔류전하를 완전히 방전시킬 것&lt;br&gt; 5. 검전기를 이용하여 작업 대상 기기가 충전되었는지를 확인할 것&lt;br&gt; 6. 전기기기등이 다른 노출 충전부와의 접촉, 유도 또는 예비동력원의 역송전 등으로 전압이 발생할 우려가 있는 경우에는 충분한 용량을 가진 단락 접지기구를 이용하여 접지할 것&lt;br&gt;③ 사업주는 제1항 각 호 외의 부분 본문에 따른 작업 중 또는 작업을 마친 후 전원을 공급하는 경우에는 작업에 종사하는 근로자 또는 그 인근에서 작업하거나 정전된 전기기기등(고정 설치된 것으로 한정한다)과 접촉할 우려가 있는 근로자에게 감전의 위험이 없도록 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 작업기구, 단락 접지기구 등을 제거하고 전기기기등이 안전하게 통전될 수 있는지를 확인할 것&lt;br&gt; 2. 모든 작업자가 작업이 완료된 전기기기등에서 떨어져 있는지를 확인할 것&lt;br&gt;▶  3. 잠금장치와 꼬리표는 설치한 &lt;strong&gt;근로자가 직접&lt;/strong&gt; 철거할 것&lt;br&gt; 4. 모든 이상 유무를 확인한 후 전기기기등의 전원을 투입할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제319조 — 정전작업 후의 조치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정전할 때 붙인 것을 송전할 때 떼어 낸다&lt;/strong&gt;는 대칭 구조다. 잠금장치와 꼬리표는 &lt;strong&gt;설치한 사람이 직접 제거&lt;/strong&gt;하는 것이 원칙이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;송전할 때는 붙이는 게 아니라 떼어 낸다&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C319%EC%A1%B0" target="_blank"&gt;제319조(정전전로에서의 전기작업)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 근로자가 노출된 충전부 또는 그 부근에서 작업함으로써 감전될 우려가 있는 경우에는 작업에 들어가기 전에 해당 전로를 차단하여야 한다. 다만, 다음 각 호의 경우에는 그러하지 아니하다.&lt;br&gt; 1. 생명유지장치, 비상경보설비, 폭발위험장소의 환기설비, 비상조명설비 등의 장치ㆍ설비의 가동이 중지되어 사고의 위험이 증가되는 경우&lt;br&gt; 2. 기기의 설계상 또는 작동상 제한으로 전로차단이 불가능한 경우&lt;br&gt; 3. 감전, 아크 등으로 인한 화상, 화재ㆍ폭발의 위험이 없는 것으로 확인된 경우&lt;br&gt;② 제1항의 전로 차단은 다음 각 호의 절차에 따라 시행하여야 한다.&lt;br&gt; 1. 전기기기등에 공급되는 모든 전원을 관련 도면, 배선도 등으로 확인할 것&lt;br&gt; 2. 전원을 차단한 후 각 단로기 등을 개방하고 확인할 것&lt;br&gt; 3. 차단장치나 단로기 등에 잠금장치 및 꼬리표를 부착할 것&lt;br&gt; 4. 개로된 전로에서 유도전압 또는 전기에너지가 축적되어 근로자에게 전기위험을 끼칠 수 있는 전기기기등은 접촉하기 전에 잔류전하를 완전히 방전시킬 것&lt;br&gt; 5. 검전기를 이용하여 작업 대상 기기가 충전되었는지를 확인할 것&lt;br&gt; 6. 전기기기등이 다른 노출 충전부와의 접촉, 유도 또는 예비동력원의 역송전 등으로 전압이 발생할 우려가 있는 경우에는 충분한 용량을 가진 단락 접지기구를 이용하여 접지할 것&lt;br&gt;③ 사업주는 제1항 각 호 외의 부분 본문에 따른 작업 중 또는 작업을 마친 후 전원을 공급하는 경우에는 작업에 종사하는 근로자 또는 그 인근에서 작업하거나 정전된 전기기기등(고정 설치된 것으로 한정한다)과 접촉할 우려가 있는 근로자에게 감전의 위험이 없도록 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 작업기구, 단락 접지기구 등을 제거하고 전기기기등이 안전하게 통전될 수 있는지를 확인할 것&lt;br&gt; 2. 모든 작업자가 작업이 완료된 전기기기등에서 떨어져 있는지를 확인할 것&lt;br&gt;▶  3. 잠금장치와 꼬리표는 설치한 &lt;strong&gt;근로자가 직접&lt;/strong&gt; 철거할 것&lt;br&gt; 4. 모든 이상 유무를 확인한 후 전기기기등의 전원을 투입할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AI80" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;계통접지의 분류&lt;/strong&gt;&lt;br&gt;뒤 글자의 뜻 — &lt;strong&gt;S 는 Separated(따로), C 는 Combined(합침)&lt;/strong&gt;. 계통접지 전체는 &lt;strong&gt;TN · TT · IT&lt;/strong&gt; 셋이고, 그 가운데 TN 만 다시 셋으로 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;TN-S · TN-C · TN-C-S&lt;/u&gt; 셋.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;계통접지의 분류&lt;/strong&gt;&lt;br&gt;뒤 글자의 뜻 — &lt;strong&gt;S는 Separated(따로), C는 Combined(합침)&lt;/strong&gt;. 계통접지 전체는 &lt;strong&gt;TN · TT · IT&lt;/strong&gt; 셋이고, 그 가운데 TN 만 다시 셋으로 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;TN-S · TN-C · TN-C-S&lt;/u&gt; 셋.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;분진 폭발위험장소의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가스는 0·1·2종, 분진은 20·21·22종&lt;/strong&gt;으로 앞에 20 을 붙인다고 새기면 대응이 쉽다. 뜻은 완전히 나란하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분진은 20 을 붙인다&lt;/u&gt; — 21종은 가스의 1종.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;분진 폭발위험장소의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가스는 0·1·2종, 분진은 20·21·22종&lt;/strong&gt;으로 앞에 20을 붙인다고 새기면 대응이 쉽다. 뜻은 완전히 나란하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분진은 20을 붙인다&lt;/u&gt; — 21종은 가스의 1종.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12142,17 +12142,17 @@
       </c>
       <c r="AG86" s="32" t="inlineStr">
         <is>
-          <t>$C_{3} H_{8} + 5 O_{2} \rightarrow 3 CO_{2} + 4 H_{2} O$ 이므로 산소가 &lt;strong&gt;5 [m³]&lt;/strong&gt; 필요하다. 공기 중 산소가 20 [%] 이므로 $5 / 0.20 = 25$ [m³] 이다.</t>
+          <t>$C_{3} H_{8} + 5 O_{2} \rightarrow 3 CO_{2} + 4 H_{2} O$이므로 산소가 &lt;strong&gt;5 [m³]&lt;/strong&gt; 필요하다. 공기 중 산소가 20 [%]이므로 $5 / 0.20 = 25$ [m³]이다.</t>
         </is>
       </c>
       <c r="AH86" s="32" t="inlineStr">
         <is>
-          <t>① 20 [m³] 는 산소량을 잘못 잡았을 때다.&lt;br&gt;③ 30 [m³] 는 산소 6몰로 계산했을 때다.&lt;br&gt;④ 35 [m³] 도 맞지 않는다.</t>
+          <t>① 20 [m³]는 산소량을 잘못 잡았을 때다.&lt;br&gt;③ 30 [m³]는 산소 6몰로 계산했을 때다.&lt;br&gt;④ 35 [m³] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI86" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;이론 공기량&lt;/strong&gt;&lt;br&gt;$C_{n} H_{m}$ 의 완전연소에 필요한 산소는 $n + m / 4$ 몰이다. 프로판은 $3 + 8 / 4 = 5$ 몰이다. &lt;strong&gt;산소량을 산소 농도로 나누면 공기량&lt;/strong&gt;이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산소 몰수 ÷ 0.21 (또는 0.20)&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;이론 공기량&lt;/strong&gt;&lt;br&gt;$C_{n} H_{m}$의 완전연소에 필요한 산소는 $n + m / 4$ 몰이다. 프로판은 $3 + 8 / 4 = 5$ 몰이다. &lt;strong&gt;산소량을 산소 농도로 나누면 공기량&lt;/strong&gt;이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산소 몰수 ÷ 0.21 (또는 0.20)&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12400,17 +12400,17 @@
       </c>
       <c r="AG88" s="32" t="inlineStr">
         <is>
-          <t>$\dfrac{100}{L} = \dfrac{75}{1.9} + \dfrac{25}{4.3} = 39.47 + 5.81 = 45.28$ 이므로 $L = 100 / 45.28 \fallingdotseq 2.2$ [vol%] 다.</t>
+          <t>$\dfrac{100}{L} = \dfrac{75}{1.9} + \dfrac{25}{4.3} = 39.47 + 5.81 = 45.28$이므로 $L = 100 / 45.28 \fallingdotseq 2.2$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH88" s="32" t="inlineStr">
         <is>
-          <t>② 3.5 는 단순 산술평균 쪽에 가깝다.&lt;br&gt;③ 22.0 은 자릿수가 어긋난다.&lt;br&gt;④ 34.7 도 어긋난다.</t>
+          <t>② 3.5는 단순 산술평균 쪽에 가깝다.&lt;br&gt;③ 22.0은 자릿수가 어긋난다.&lt;br&gt;④ 34.7 도 어긋난다.</t>
         </is>
       </c>
       <c r="AI88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;르 샤틀리에의 혼합가스 폭발범위&lt;/strong&gt;&lt;br&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$ 다. &lt;strong&gt;하한이 낮은 성분이 결과를 크게 끌어내린다&lt;/strong&gt;. 여기서도 1.9 쪽이 75 [%] 를 차지해 답이 2.2 로 낮게 나왔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;몫을 더한 뒤 뒤집는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;르 샤틀리에의 혼합가스 폭발범위&lt;/strong&gt;&lt;br&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$다. &lt;strong&gt;하한이 낮은 성분이 결과를 크게 끌어내린다&lt;/strong&gt;. 여기서도 1.9 쪽이 75 [%]를 차지해 답이 2.2로 낮게 나왔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;몫을 더한 뒤 뒤집는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="AI89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자연발화의 방지법&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt; 일 때 일어난다. 방지법은 &lt;strong&gt;발열을 줄이거나(온도·수분·산소를 끊고) 방열을 늘리는 것(통풍·얇게 쌓기)&lt;/strong&gt; 둘뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습도는 낮게&lt;/u&gt; — 「높은 곳에」가 나오면 오답.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자연발화의 방지법&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt;일 때 일어난다. 방지법은 &lt;strong&gt;발열을 줄이거나(온도·수분·산소를 끊고) 방열을 늘리는 것(통풍·얇게 쌓기)&lt;/strong&gt; 둘뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습도는 낮게&lt;/u&gt; — 「높은 곳에」가 나오면 오답.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="AG90" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;이황화탄소는 오히려 물속에 저장&lt;/strong&gt; 한다. 물보다 무겁고 녹지 않아 물이 증기 발생을 막아 준다.</t>
+          <t>&lt;strong&gt;이황화탄소는 오히려 물속에 저장&lt;/strong&gt;한다. 물보다 무겁고 녹지 않아 물이 증기 발생을 막아 준다.</t>
         </is>
       </c>
       <c r="AH90" s="32" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="AG92" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;칼륨·나트륨&lt;/strong&gt;이다. 나머지 셋은 모두 &lt;strong&gt;폭발성 물질 및 유기과산화물&lt;/strong&gt;에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전보건규칙 별표1 — 위험물질 일곱 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발성 물질 및 유기과산화물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질산에스테르류 · 니트로화합물 · 니트로소화합물 · 아조화합물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;산소 없이도 터진다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물반응성 물질 및 인화성 고체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;리튬 · 칼륨 · 나트륨 · 황 · 황린 · 황화인 · 적린&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물과 반응하거나 쉽게 붙는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산화성 액체 및 산화성 고체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;염소산 · 과염소산 · 과산화물 · 질산&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;남을 태운다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화성 액체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;에틸에테르 · 가솔린 · 아세톤&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;상온에서 액체&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화성 가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수소 · 아세틸렌 · 에틸렌 · 메탄&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;상온에서 기체&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;농도 20 [%] 이상 염산·황산·질산 등&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;살을 상하게 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;급성 독성 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;LD50 이 일정 값 이하&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;적은 양으로 죽는다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;칼륨·나트륨&lt;/strong&gt;이다. 나머지 셋은 모두 &lt;strong&gt;폭발성 물질 및 유기과산화물&lt;/strong&gt;에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전보건규칙 별표1 — 위험물질 일곱 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발성 물질 및 유기과산화물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질산에스테르류 · 니트로화합물 · 니트로소화합물 · 아조화합물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;산소 없이도 터진다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물반응성 물질 및 인화성 고체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;리튬 · 칼륨 · 나트륨 · 황 · 황린 · 황화인 · 적린&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물과 반응하거나 쉽게 붙는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산화성 액체 및 산화성 고체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;염소산 · 과염소산 · 과산화물 · 질산&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;남을 태운다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화성 액체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;에틸에테르 · 가솔린 · 아세톤&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;상온에서 액체&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화성 가스&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수소 · 아세틸렌 · 에틸렌 · 메탄&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;상온에서 기체&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;농도 20 [%] 이상 염산·황산·질산 등&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;살을 상하게 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;급성 독성 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;LD50이 일정 값 이하&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;적은 양으로 죽는다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH92" s="32" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="AG93" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인화칼슘(Ca₃P₂)&lt;/strong&gt;이다. $\mathrm{Ca}_{3} P_{2} + 6 H_{2} O \rightarrow 3 \mathrm{Ca} ( OH )_{2} + 2 PH_{3}$ 로 &lt;strong&gt;포스핀(PH₃)&lt;/strong&gt;이 나온다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;물과 만나면 무엇이 나오나&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;생성 가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화칼슘 Ca₃P₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;포스핀 PH₃&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;맹독성 · 자연발화성&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화칼슘(카바이드) CaC₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세틸렌 C₂H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;폭발범위 2.5~81 [%]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화알루미늄 Al₄C₃&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;메탄 CH₄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;금속 나트륨 · 칼륨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;격렬한 발열&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소화리튬 LiH&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;알루미늄 분말&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;인화칼슘(Ca₃P₂)&lt;/strong&gt;이다. $\mathrm{Ca}_{3} P_{2} + 6 H_{2} O \rightarrow 3 \mathrm{Ca} ( OH )_{2} + 2 PH_{3}$로 &lt;strong&gt;포스핀(PH₃)&lt;/strong&gt;이 나온다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;물과 만나면 무엇이 나오나&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;생성 가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화칼슘 Ca₃P₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;포스핀 PH₃&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;맹독성 · 자연발화성&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화칼슘(카바이드) CaC₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세틸렌 C₂H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;폭발범위 2.5~81 [%]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화알루미늄 Al₄C₃&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;메탄 CH₄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;금속 나트륨 · 칼륨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;격렬한 발열&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소화리튬 LiH&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;알루미늄 분말&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH93" s="32" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
-          <t>① 암모니아는 25 [ppm] 이다.&lt;br&gt;③ 톨루엔은 50 [ppm] 이다.&lt;br&gt;④ 황화수소는 10 [ppm] 이다.</t>
+          <t>① 암모니아는 25 [ppm]이다.&lt;br&gt;③ 톨루엔은 50 [ppm]이다.&lt;br&gt;④ 황화수소는 10 [ppm]이다.</t>
         </is>
       </c>
       <c r="AI94" s="32" t="inlineStr">
@@ -13561,17 +13561,17 @@
       </c>
       <c r="AG97" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;10 [m] 이상&lt;/strong&gt;이다. 서로 다른 단위공정 사이는 바깥 면끼리 10 [m] 를 띄운다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;화학설비의 안전거리 (규칙 별표8)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준점&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위공정시설·설비 ↔ 다른 단위공정시설·설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바깥 면끼리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;플레어스택 ↔ 위험물 저장탱크·유해물질 취급설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;반경 20 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;플레어스택 중심&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물 저장탱크 ↔ 단위공정시설·설비, 보일러, 가열로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;탱크 바깥 면에서 20 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사무실·연구실·실험실·정비실 ↔ 위험물 취급설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바깥 면에서 20 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;10 [m] 이상&lt;/strong&gt;이다. 서로 다른 단위공정 사이는 바깥 면끼리 10 [m]를 띄운다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;화학설비의 안전거리 (규칙 별표8)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준점&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위공정시설·설비 ↔ 다른 단위공정시설·설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바깥 면끼리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;플레어스택 ↔ 위험물 저장탱크·유해물질 취급설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;반경 20 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;플레어스택 중심&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물 저장탱크 ↔ 단위공정시설·설비, 보일러, 가열로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;탱크 바깥 면에서 20 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사무실·연구실·실험실·정비실 ↔ 위험물 취급설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바깥 면에서 20 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH97" s="32" t="inlineStr">
         <is>
-          <t>① 5 [m] 는 기준에 못 미친다.&lt;br&gt;③ 15 [m] 라는 기준은 없다.&lt;br&gt;④ 20 [m] 는 플레어스택·저장탱크·사무실 기준이다.</t>
+          <t>① 5 [m]는 기준에 못 미친다.&lt;br&gt;③ 15 [m]라는 기준은 없다.&lt;br&gt;④ 20 [m]는 플레어스택·저장탱크·사무실 기준이다.</t>
         </is>
       </c>
       <c r="AI97" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 별표8 — 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;10 [m] 는 단위공정끼리 하나뿐&lt;/strong&gt;이고, &lt;strong&gt;나머지 셋은 모두 20 [m]&lt;/strong&gt;다. 이렇게 갈라 두면 숫자가 섞이지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;단위공정끼리만 10, 나머지는 20&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 8&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 별표8 — 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;10 [m]는 단위공정끼리 하나뿐&lt;/strong&gt;이고, &lt;strong&gt;나머지 셋은 모두 20 [m]&lt;/strong&gt;다. 이렇게 갈라 두면 숫자가 섞이지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;단위공정끼리만 10, 나머지는 20&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 8&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="AG98" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안을 열어 봐야 알 수 있는 것&lt;/strong&gt;이 개방점검이다. &lt;strong&gt;생성물과 부착물에 의한 오염&lt;/strong&gt;은 뜯어야 보인다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;열교환기의 일상점검과 개방점검&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;일상점검 (겉에서 본다)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;개방점검 (뜯어서 본다)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;항목&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보냉재의 파손&lt;/u&gt; · &lt;u&gt;플랜지부·용접부의 누출&lt;/u&gt; · &lt;u&gt;기초볼트의 체결 상태&lt;/u&gt; · 도장의 노후&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생성물·부착물에 의한 오염&lt;/u&gt; · &lt;u&gt;부식과 두께 감소&lt;/u&gt; · 용접선의 상황 · 라이닝·개스킷 손상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;특징&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전 중에도 할 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전을 멈추고 분해&lt;/u&gt; 해야 한다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안을 열어 봐야 알 수 있는 것&lt;/strong&gt;이 개방점검이다. &lt;strong&gt;생성물과 부착물에 의한 오염&lt;/strong&gt;은 뜯어야 보인다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;열교환기의 일상점검과 개방점검&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;일상점검 (겉에서 본다)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;개방점검 (뜯어서 본다)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;항목&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보냉재의 파손&lt;/u&gt; · &lt;u&gt;플랜지부·용접부의 누출&lt;/u&gt; · &lt;u&gt;기초볼트의 체결 상태&lt;/u&gt; · 도장의 노후&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생성물·부착물에 의한 오염&lt;/u&gt; · &lt;u&gt;부식과 두께 감소&lt;/u&gt; · 용접선의 상황 · 라이닝·개스킷 손상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;특징&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전 중에도 할 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전을 멈추고 분해&lt;/u&gt;해야 한다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH98" s="32" t="inlineStr">
@@ -13948,17 +13948,17 @@
       </c>
       <c r="AG100" s="32" t="inlineStr">
         <is>
-          <t>$\mathrm{MOC} = \text{폭발하한계} \times \text{산소의 양론계수}$ 다. $C_{4} H_{10} + 6.5 O_{2} \rightarrow 4 CO_{2} + 5 H_{2} O$ 이므로 계수는 6.5 다. $1.6 \times 6.5 = 10.4$ [vol%] 다.</t>
+          <t>$\mathrm{MOC} = \text{폭발하한계} \times \text{산소의 양론계수}$다. $C_{4} H_{10} + 6.5 O_{2} \rightarrow 4 CO_{2} + 5 H_{2} O$이므로 계수는 6.5다. $1.6 \times 6.5 = 10.4$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH100" s="32" t="inlineStr">
         <is>
-          <t>① 5.6 [vol%] 는 계수를 3.5 로 잡았을 때 쪽이다.&lt;br&gt;② 7.8 [vol%] 는 계수를 5 로 잡았을 때다.&lt;br&gt;④ 14.1 [vol%] 도 맞지 않는다.</t>
+          <t>① 5.6 [vol%]는 계수를 3.5로 잡았을 때 쪽이다.&lt;br&gt;② 7.8 [vol%]는 계수를 5로 잡았을 때다.&lt;br&gt;④ 14.1 [vol%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최소산소농도(MOC)&lt;/strong&gt;&lt;br&gt;산소의 양론계수는 $n + m / 4$ 로 구한다. 부탄은 $4 + 10 / 4 = 6.5$ 다. 실무에서는 &lt;strong&gt;MOC 보다 4 [%] 정도 더 낮게&lt;/strong&gt; 잡아 불활성화한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\mathrm{MOC} = \mathrm{LFL} \times ( n + m / 4 )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;최소산소농도(MOC)&lt;/strong&gt;&lt;br&gt;산소의 양론계수는 $n + m / 4$로 구한다. 부탄은 $4 + 10 / 4 = 6.5$다. 실무에서는 &lt;strong&gt;MOC보다 4 [%] 정도 더 낮게&lt;/strong&gt; 잡아 불활성화한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\mathrm{MOC} = \mathrm{LFL} \times ( n + m / 4 )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14077,17 +14077,17 @@
       </c>
       <c r="AG101" s="32" t="inlineStr">
         <is>
-          <t>가솔린의 폭발범위는 &lt;strong&gt;1.4 ~ 7.6 [vol%]&lt;/strong&gt;다. &lt;strong&gt;하한이 1.4 [vol%] 로 낮아&lt;/strong&gt; 조금만 새어도 폭발 농도에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 물질의 폭발범위 [vol%]&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;폭발범위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;위험도 H&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 ~ 81&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;31.4&lt;/u&gt; — 가장 크다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 ~ 75&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;17.8&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이황화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.2 ~ 44&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;35.7&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일산화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;12.5 ~ 74&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4.92&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가솔린&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.4 ~ 7.6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4.43&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프로판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.1 ~ 9.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;3.5&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 ~ 15&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2.0&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>가솔린의 폭발범위는 &lt;strong&gt;1.4 ~ 7.6 [vol%]&lt;/strong&gt;다. &lt;strong&gt;하한이 1.4 [vol%]로 낮아&lt;/strong&gt; 조금만 새어도 폭발 농도에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 물질의 폭발범위 [vol%]&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;폭발범위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;위험도 H&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 ~ 81&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;31.4&lt;/u&gt; — 가장 크다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 ~ 75&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;17.8&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이황화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.2 ~ 44&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;35.7&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일산화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;12.5 ~ 74&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4.92&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가솔린&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.4 ~ 7.6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4.43&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프로판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.1 ~ 9.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;3.5&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 ~ 15&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2.0&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH101" s="32" t="inlineStr">
         <is>
-          <t>① 2.7 ~ 27.8 [vol%] 는 산화에틸렌 쪽에 가깝다.&lt;br&gt;② 3.4 ~ 11.8 [vol%] 도 가솔린 값이 아니다.&lt;br&gt;④ 5.1 ~ 18.2 [vol%] 는 메탄 쪽에 가깝다.</t>
+          <t>① 2.7 ~ 27.8 [vol%]는 산화에틸렌 쪽에 가깝다.&lt;br&gt;② 3.4 ~ 11.8 [vol%] 도 가솔린 값이 아니다.&lt;br&gt;④ 5.1 ~ 18.2 [vol%]는 메탄 쪽에 가깝다.</t>
         </is>
       </c>
       <c r="AI101" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;주요 가스의 폭발범위&lt;/strong&gt;&lt;br&gt;가솔린은 &lt;strong&gt;범위 자체는 좁지만 하한이 1.4 [vol%] 로 낮아&lt;/strong&gt; 실제로는 다루기 까다롭다. &lt;strong&gt;인화점도 −43 [℃]&lt;/strong&gt;라 상온에서 늘 증기가 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가솔린 1.4 ~ 7.6&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;주요 가스의 폭발범위&lt;/strong&gt;&lt;br&gt;가솔린은 &lt;strong&gt;범위 자체는 좁지만 하한이 1.4 [vol%]로 낮아&lt;/strong&gt; 실제로는 다루기 까다롭다. &lt;strong&gt;인화점도 −43 [℃]&lt;/strong&gt;라 상온에서 늘 증기가 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가솔린 1.4 ~ 7.6&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14468,12 +14468,12 @@
       </c>
       <c r="AG104" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;A 는 75, B 는 40&lt;/strong&gt;이다. 기울기 75° 이하, 작업발판 폭 40 [cm] 이상이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;말비계의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재와 수평면의 기울기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;A&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 2 [m] 초과 시 작업발판 폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재 사이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보조부재&lt;/u&gt; 설치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다리가 벌어지지 않게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밑부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미끄럼 방지장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;A는 75, B는 40&lt;/strong&gt;이다. 기울기 75° 이하, 작업발판 폭 40 [cm] 이상이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;말비계의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재와 수평면의 기울기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;A&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 2 [m] 초과 시 작업발판 폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재 사이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보조부재&lt;/u&gt; 설치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다리가 벌어지지 않게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밑부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미끄럼 방지장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH104" s="32" t="inlineStr">
         <is>
-          <t>① B 가 30 [cm] 이면 작업발판 폭 기준에 못 미친다.&lt;br&gt;③ A 가 85° 면 너무 서서 넘어지기 쉽다.&lt;br&gt;④ A·B 둘 다 어긋난다.</t>
+          <t>① B가 30 [cm] 이면 작업발판 폭 기준에 못 미친다.&lt;br&gt;③ A가 85° 면 너무 서서 넘어지기 쉽다.&lt;br&gt;④ A·B 둘 다 어긋난다.</t>
         </is>
       </c>
       <c r="AI104" s="32" t="inlineStr">
@@ -14601,17 +14601,17 @@
       </c>
       <c r="AG105" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;A 는 4, B 는 10, C 는 10&lt;/strong&gt;이다. &lt;strong&gt;좁고 높은 비계&lt;/strong&gt;는 넘어지기 쉬워 버팀기둥으로 붙잡아 준다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관틀비계의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀기둥 설치 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;띠장방향 길이 4 [m] 이하 + 높이 10 [m] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;좁고 높으면&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀기둥 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 이내마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;띠장방향으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주틀 간 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;높이 20 [m] 초과 시&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주틀 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;높이 20 [m] 초과 시&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수직방향 벽이음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [m] 마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수평방향 벽이음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8 [m] 마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;A는 4, B는 10, C는 10&lt;/strong&gt;이다. &lt;strong&gt;좁고 높은 비계&lt;/strong&gt;는 넘어지기 쉬워 버팀기둥으로 붙잡아 준다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관틀비계의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀기둥 설치 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;띠장방향 길이 4 [m] 이하 + 높이 10 [m] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;좁고 높으면&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀기둥 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 이내마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;띠장방향으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주틀 간 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;높이 20 [m] 초과 시&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주틀 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;높이 20 [m] 초과 시&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수직방향 벽이음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [m] 마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수평방향 벽이음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8 [m] 마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH105" s="32" t="inlineStr">
         <is>
-          <t>① C 가 5 [m] 라는 기준은 없다.&lt;br&gt;③ A 가 5 [m] 라는 기준도 없다.&lt;br&gt;④ A·C 둘 다 어긋난다.</t>
+          <t>① C가 5 [m]라는 기준은 없다.&lt;br&gt;③ A가 5 [m]라는 기준도 없다.&lt;br&gt;④ A·C 둘 다 어긋난다.</t>
         </is>
       </c>
       <c r="AI105" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제62조 — 강관틀비계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;높이 20 [m] 를 넘거나 중량물을 다루면&lt;/strong&gt; 주틀 간 간격을 &lt;strong&gt;1.8 [m] 이하&lt;/strong&gt;, 주틀 높이를 &lt;strong&gt;2 [m] 이하&lt;/strong&gt;로 줄인다. 벽이음은 &lt;strong&gt;수직 6 · 수평 8&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;4 · 10 · 10&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C62%EC%A1%B0" target="_blank"&gt;제62조(강관틀비계)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 강관틀 비계를 조립하여 사용하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 비계기둥의 밑둥에는 밑받침 철물을 사용하여야 하며 밑받침에 고저차(高低差)가 있는 경우에는 조절형 밑받침철물을 사용하여 각각의 강관틀비계가 항상 수평 및 수직을 유지하도록 할 것&lt;br&gt;▶  2. 높이가 20미터를 초과하거나 중량물의 적재를 수반하는 작업을 할 경우에는 주틀 간의 간격을 1.8미터 이하로 할 것&lt;br&gt; 3. 주틀 간에 교차 가새를 설치하고 최상층 및 5층 이내마다 수평재를 설치할 것&lt;br&gt; 4. 수직방향으로 6미터, 수평방향으로 8미터 이내마다 벽이음을 할 것&lt;br&gt; 5. 길이가 띠장 방향으로 4미터 이하이고 높이가 10미터를 초과하는 경우에는 10미터 이내마다 띠장 방향으로 버팀기둥을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제62조 — 강관틀비계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;높이 20 [m]를 넘거나 중량물을 다루면&lt;/strong&gt; 주틀 간 간격을 &lt;strong&gt;1.8 [m] 이하&lt;/strong&gt;, 주틀 높이를 &lt;strong&gt;2 [m] 이하&lt;/strong&gt;로 줄인다. 벽이음은 &lt;strong&gt;수직 6 · 수평 8&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;4 · 10 · 10&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C62%EC%A1%B0" target="_blank"&gt;제62조(강관틀비계)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 강관틀 비계를 조립하여 사용하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 비계기둥의 밑둥에는 밑받침 철물을 사용하여야 하며 밑받침에 고저차(高低差)가 있는 경우에는 조절형 밑받침철물을 사용하여 각각의 강관틀비계가 항상 수평 및 수직을 유지하도록 할 것&lt;br&gt;▶  2. 높이가 20미터를 초과하거나 중량물의 적재를 수반하는 작업을 할 경우에는 주틀 간의 간격을 1.8미터 이하로 할 것&lt;br&gt; 3. 주틀 간에 교차 가새를 설치하고 최상층 및 5층 이내마다 수평재를 설치할 것&lt;br&gt; 4. 수직방향으로 6미터, 수평방향으로 8미터 이내마다 벽이음을 할 것&lt;br&gt; 5. 길이가 띠장 방향으로 4미터 이하이고 높이가 10미터를 초과하는 경우에는 10미터 이내마다 띠장 방향으로 버팀기둥을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -15633,7 +15633,7 @@
       </c>
       <c r="AG113" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;고정식은 90° 이하&lt;/strong&gt;다. 일반 사다리식 통로의 &lt;strong&gt;75° 이하&lt;/strong&gt;와 다르다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;사다리식 통로의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기울기 — 일반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기울기 — 고정식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업발판 40 과 다르다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발판과 벽 사이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;발이 들어갈 틈&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상단 돌출&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;붙잡을 곳&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;길이 10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m] 이내마다 계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;고정식은 90° 이하&lt;/strong&gt;다. 일반 사다리식 통로의 &lt;strong&gt;75° 이하&lt;/strong&gt;와 다르다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;사다리식 통로의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기울기 — 일반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기울기 — 고정식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업발판 40과 다르다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발판과 벽 사이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;발이 들어갈 틈&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상단 돌출&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;붙잡을 곳&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;길이 10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m] 이내마다 계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH113" s="32" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="AI116" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;용접부의 비파괴검사&lt;/strong&gt;&lt;br&gt;엄밀히는 &lt;strong&gt;자분탐상과 침투탐상은 표면 검사&lt;/strong&gt;라 「내부결함 검사」로 보기 어렵다. 확정답안이 ①③④를 모두 정답으로 처리한 까닭이 여기 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내부는 RT · UT, 표면은 MT · PT&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항은 가답안이 ①이었으나 &lt;u&gt;확정답안에서 ①③④가 모두 정답 처리&lt;/u&gt; 됐다. &lt;u&gt;자분탐상(③)과 침투탐상(④)은 표면 결함 검사&lt;/u&gt;라 「내부결함 검사」라는 물음에 맞지 않기 때문이다. &lt;u&gt;내부결함을 보는 것은 방사선투과와 초음파탐상 둘뿐&lt;/u&gt; 이라고 정리해 두면 어느 쪽으로 물어도 풀린다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;용접부의 비파괴검사&lt;/strong&gt;&lt;br&gt;엄밀히는 &lt;strong&gt;자분탐상과 침투탐상은 표면 검사&lt;/strong&gt;라 「내부결함 검사」로 보기 어렵다. 확정답안이 ①③④를 모두 정답으로 처리한 까닭이 여기 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내부는 RT · UT, 표면은 MT · PT&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항은 가답안이 ①이었으나 &lt;u&gt;확정답안에서 ①③④가 모두 정답 처리&lt;/u&gt;됐다. &lt;u&gt;자분탐상(③)과 침투탐상(④)은 표면 결함 검사&lt;/u&gt;라 「내부결함 검사」라는 물음에 맞지 않기 때문이다. &lt;u&gt;내부결함을 보는 것은 방사선투과와 초음파탐상 둘뿐&lt;/u&gt; 이라고 정리해 두면 어느 쪽으로 물어도 풀린다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="AH117" s="32" t="inlineStr">
         <is>
-          <t>② 1.99 [%] 는 다른 공사종류의 값이다.&lt;br&gt;③ 2.35 [%] 도 다른 공사종류의 값이다.&lt;br&gt;④ 1.57 [%] 도 이 구간의 값이 아니다.</t>
+          <t>② 1.99 [%]는 다른 공사종류의 값이다.&lt;br&gt;③ 2.35 [%] 도 다른 공사종류의 값이다.&lt;br&gt;④ 1.57 [%] 도 이 구간의 값이 아니다.</t>
         </is>
       </c>
       <c r="AI117" s="32" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="AH118" s="32" t="inlineStr">
         <is>
-          <t>① 0.2 [m] 라는 기준은 없다.&lt;br&gt;③ 0.4 [m] 도 기준이 아니다.&lt;br&gt;④ 0.5 [m] 도 기준이 아니다.</t>
+          <t>① 0.2 [m]라는 기준은 없다.&lt;br&gt;③ 0.4 [m] 도 기준이 아니다.&lt;br&gt;④ 0.5 [m] 도 기준이 아니다.</t>
         </is>
       </c>
       <c r="AI118" s="32" t="inlineStr">
@@ -16528,7 +16528,7 @@
       </c>
       <c r="AG120" s="32" t="inlineStr">
         <is>
-          <t>거꾸로다. 와이어로프는 &lt;strong&gt;클립과 섀클 등의 기구를 사용하여 고정&lt;/strong&gt; 해야 한다. 그냥 묶어서는 버티지 못한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;타워크레인의 와이어로프 지지 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지지프레임&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전용 지지프레임&lt;/u&gt; 사용&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치각도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수평면에서 60° 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지지점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4개소 이상&lt;/u&gt; · 같은 각도로&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고정 방법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;클립·섀클 등으로 고정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「하지 않도록」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가공전선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;근접하지 않게&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>거꾸로다. 와이어로프는 &lt;strong&gt;클립과 섀클 등의 기구를 사용하여 고정&lt;/strong&gt;해야 한다. 그냥 묶어서는 버티지 못한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;타워크레인의 와이어로프 지지 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지지프레임&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전용 지지프레임&lt;/u&gt; 사용&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치각도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수평면에서 60° 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지지점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4개소 이상&lt;/u&gt; · 같은 각도로&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고정 방법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;클립·섀클 등으로 고정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「하지 않도록」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가공전선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;근접하지 않게&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH120" s="32" t="inlineStr">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="AI120" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제142조 — 타워크레인의 지지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;지지벽체가 있으면 벽체에, 없으면 와이어로프로&lt;/strong&gt; 지지한다. 벽체 지지는 &lt;strong&gt;설치각도 4개소 이상 · 콘크리트 구조물에 고정&lt;/strong&gt; 하는 것이 원칙이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;60° 이내 · 4개소 이상 · 클립으로 고정&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C142%EC%A1%B0" target="_blank"&gt;제142조(타워크레인의 지지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 타워크레인을 자립고(自立高) 이상의 높이로 설치하는 경우 건축물 등의 벽체에 지지하도록 하여야 한다. 다만, 지지할 벽체가 없는 등 부득이한 경우에는 와이어로프에 의하여 지지할 수 있다. &amp;lt;개정 2013.3.21&amp;gt;&lt;br&gt;② 사업주는 타워크레인을 벽체에 지지하는 경우 다음 각 호의 사항을 준수하여야 한다. &amp;lt;개정 2019.1.31, 2019.12.26&amp;gt;&lt;br&gt; 1. 「산업안전보건법 시행규칙」 제110조제1항제2호에 따른 서면심사에 관한 서류(「건설기계관리법」 제18조에 따른 형식승인서류를 포함한다) 또는 제조사의 설치작업설명서 등에 따라 설치할 것&lt;br&gt; 2. 제1호의 서면심사 서류 등이 없거나 명확하지 아니한 경우에는 「국가기술자격법」에 따른 건축구조ㆍ건설기계ㆍ기계안전ㆍ건설안전기술사 또는 건설안전분야 산업안전지도사의 확인을 받아 설치하거나 기종별ㆍ모델별 공인된 표준방법으로 설치할 것&lt;br&gt;▶  3. &lt;strong&gt;콘크리트구조물에 고정&lt;/strong&gt;시키는 경우에는 매립이나 관통 또는 이와 같은 수준 이상의 방법으로 충분히 지지되도록 할 것&lt;br&gt; 4. 건축 중인 시설물에 지지하는 경우에는 그 시설물의 구조적 안정성에 영향이 없도록 할 것&lt;br&gt;③ 사업주는 타워크레인을 와이어로프로 지지하는 경우 다음 각 호의 사항을 준수해야 한다. &amp;lt;개정 2013.3.21, 2019.10.15, 2022.10.18&amp;gt;&lt;br&gt; 1. 제2항제1호 또는 제2호의 조치를 취할 것&lt;br&gt; 2. 와이어로프를 고정하기 위한 전용 지지프레임을 사용할 것&lt;br&gt;▶  3. 와이어로프 설치각도는 수평면에서 60도 이내로 하되, 지지점은 &lt;strong&gt;4개소 이상&lt;/strong&gt;으로 하고, 같은 각도로 설치할 것&lt;br&gt;▶  4. 와이어로프와 그 고정부위는 충분한 강도와 장력을 갖도록 설치하고, 와이어로프를 클립ㆍ샤클(shackle, 연결고리) 등의 고정&lt;strong&gt;기구를 사용하여&lt;/strong&gt; 견고하게 고정시켜 풀리지 않도록 하며, 사용 중에는 충분한 강도와 장력을 유지하도록 할 것. 이 경우 클립ㆍ샤클 등의 고정기구는 한국산업표준 제품이거나 한국산업표준이 없는 제품의 경우에는 이에 준하는 규격을 갖춘 제품이어야 한다.&lt;br&gt; 5. 와이어로프가 가공전선(架空電線)에 근접하지 않도록 할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제142조 — 타워크레인의 지지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;지지벽체가 있으면 벽체에, 없으면 와이어로프로&lt;/strong&gt; 지지한다. 벽체 지지는 &lt;strong&gt;설치각도 4개소 이상 · 콘크리트 구조물에 고정&lt;/strong&gt;하는 것이 원칙이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;60° 이내 · 4개소 이상 · 클립으로 고정&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C142%EC%A1%B0" target="_blank"&gt;제142조(타워크레인의 지지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 타워크레인을 자립고(自立高) 이상의 높이로 설치하는 경우 건축물 등의 벽체에 지지하도록 하여야 한다. 다만, 지지할 벽체가 없는 등 부득이한 경우에는 와이어로프에 의하여 지지할 수 있다. &amp;lt;개정 2013.3.21&amp;gt;&lt;br&gt;② 사업주는 타워크레인을 벽체에 지지하는 경우 다음 각 호의 사항을 준수하여야 한다. &amp;lt;개정 2019.1.31, 2019.12.26&amp;gt;&lt;br&gt; 1. 「산업안전보건법 시행규칙」 제110조제1항제2호에 따른 서면심사에 관한 서류(「건설기계관리법」 제18조에 따른 형식승인서류를 포함한다) 또는 제조사의 설치작업설명서 등에 따라 설치할 것&lt;br&gt; 2. 제1호의 서면심사 서류 등이 없거나 명확하지 아니한 경우에는 「국가기술자격법」에 따른 건축구조ㆍ건설기계ㆍ기계안전ㆍ건설안전기술사 또는 건설안전분야 산업안전지도사의 확인을 받아 설치하거나 기종별ㆍ모델별 공인된 표준방법으로 설치할 것&lt;br&gt;▶  3. &lt;strong&gt;콘크리트구조물에 고정&lt;/strong&gt;시키는 경우에는 매립이나 관통 또는 이와 같은 수준 이상의 방법으로 충분히 지지되도록 할 것&lt;br&gt; 4. 건축 중인 시설물에 지지하는 경우에는 그 시설물의 구조적 안정성에 영향이 없도록 할 것&lt;br&gt;③ 사업주는 타워크레인을 와이어로프로 지지하는 경우 다음 각 호의 사항을 준수해야 한다. &amp;lt;개정 2013.3.21, 2019.10.15, 2022.10.18&amp;gt;&lt;br&gt; 1. 제2항제1호 또는 제2호의 조치를 취할 것&lt;br&gt; 2. 와이어로프를 고정하기 위한 전용 지지프레임을 사용할 것&lt;br&gt;▶  3. 와이어로프 설치각도는 수평면에서 60도 이내로 하되, 지지점은 &lt;strong&gt;4개소 이상&lt;/strong&gt;으로 하고, 같은 각도로 설치할 것&lt;br&gt;▶  4. 와이어로프와 그 고정부위는 충분한 강도와 장력을 갖도록 설치하고, 와이어로프를 클립ㆍ샤클(shackle, 연결고리) 등의 고정&lt;strong&gt;기구를 사용하여&lt;/strong&gt; 견고하게 고정시켜 풀리지 않도록 하며, 사용 중에는 충분한 강도와 장력을 유지하도록 할 것. 이 경우 클립ㆍ샤클 등의 고정기구는 한국산업표준 제품이거나 한국산업표준이 없는 제품의 경우에는 이에 준하는 규격을 갖춘 제품이어야 한다.&lt;br&gt; 5. 와이어로프가 가공전선(架空電線)에 근접하지 않도록 할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="AG121" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;굴착 깊이가 20 [m] 를 초과할 때&lt;/strong&gt; 통신설비를 설치한다. 10 [m] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;잠함·우물통 내부 굴착작업의 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소 농도 측정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;측정자를 &lt;u&gt;지명&lt;/u&gt; 하여&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;산소 결핍 우려 시&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;송기 설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;결핍이 인정되면 &lt;u&gt;공기 공급&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승강 설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전하게 오르내릴 수 있게&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통신설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;굴착 깊이 20 [m] 초과&lt;/u&gt; 시&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;굴착 깊이가 20 [m]를 초과할 때&lt;/strong&gt; 통신설비를 설치한다. 10 [m]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;잠함·우물통 내부 굴착작업의 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소 농도 측정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;측정자를 &lt;u&gt;지명&lt;/u&gt;하여&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;산소 결핍 우려 시&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;송기 설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;결핍이 인정되면 &lt;u&gt;공기 공급&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승강 설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전하게 오르내릴 수 있게&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통신설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;굴착 깊이 20 [m] 초과&lt;/u&gt; 시&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH121" s="32" t="inlineStr">
